--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -626,10 +626,10 @@
         <v>309</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>131.3333333333333</v>
+        <v>130.6666666666667</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -659,10 +659,10 @@
         <v>252</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,59 +676,59 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Koyyagurapadu B.O</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Vinnakota B.O</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>182</v>
       </c>
-      <c r="C4" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>148</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>98.66666666666667</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>2</v>
+      <c r="C4" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>105.3333333333333</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -742,26 +742,26 @@
         <v>150</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>94</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         <v>150</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>93.33333333333333</v>
+        <v>92.66666666666666</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         <v>150</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>92.66666666666666</v>
+        <v>91.33333333333333</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>64</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
         <v>150</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>83.33333333333334</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>25</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -907,92 +907,92 @@
         <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>81.33333333333333</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>188</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Pedapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>134</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>116</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>77.33333333333333</v>
+      <c r="B12" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>81.33333333333333</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         <v>150</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>76.66666666666667</v>
+        <v>78.66666666666666</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -1022,10 +1022,10 @@
         <v>126</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -1039,26 +1039,26 @@
         <v>150</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>76</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -1072,26 +1072,26 @@
         <v>150</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>73.33333333333333</v>
+        <v>74</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -1105,26 +1105,26 @@
         <v>150</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>72</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -1138,26 +1138,26 @@
         <v>150</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
         <v>150</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1204,26 +1204,26 @@
         <v>150</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>70.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1237,26 +1237,26 @@
         <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>68</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1270,26 +1270,26 @@
         <v>150</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>66.66666666666666</v>
+        <v>70</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1303,26 +1303,26 @@
         <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>66.66666666666666</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,26 +1336,26 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>66.66666666666666</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,26 +1369,26 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>66</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>66</v>
+        <v>64.66666666666666</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>60.66666666666667</v>
+        <v>62</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>23</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>44</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,158 +1600,158 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
+          <t>Nandivada B.O</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>55.33333333333334</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Dondapadu B.O</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>52.66666666666666</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Pedaparupudi B.O</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
           <t>Tenneru B.O</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
+      <c r="B35" s="13" t="n">
         <v>246</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C35" s="13" t="n">
         <v>171</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D35" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H32" s="15" t="n">
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I32" s="11" t="n">
+      <c r="I35" s="11" t="n">
         <v>75</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Komaravolu B.O</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="n">
-        <v>158</v>
-      </c>
-      <c r="C33" s="17" t="n">
-        <v>85</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G33" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H33" s="19" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>Unikili B.O</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="n">
-        <v>90</v>
-      </c>
-      <c r="C34" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G34" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H34" s="19" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Ponukumadu B.O</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="n">
-        <v>94</v>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C36" s="17" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
@@ -1765,26 +1765,26 @@
         <v>150</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>46.66666666666666</v>
+        <v>49.33333333333334</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="C37" s="17" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
@@ -1798,26 +1798,26 @@
         <v>150</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>44</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C38" s="17" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         <v>150</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C39" s="17" t="n">
         <v>31</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -1864,26 +1864,26 @@
         <v>150</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>42.66666666666667</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -1897,26 +1897,26 @@
         <v>150</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>42</v>
+        <v>44.66666666666666</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
@@ -1930,26 +1930,26 @@
         <v>150</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>40.66666666666666</v>
+        <v>44</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -1963,59 +1963,59 @@
         <v>150</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>42</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="I43" s="11" t="n">
         <v>87</v>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>58</v>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>38.66666666666666</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -2029,26 +2029,26 @@
         <v>150</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>36.66666666666666</v>
+        <v>42</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -2062,26 +2062,26 @@
         <v>150</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>42</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -2095,26 +2095,26 @@
         <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>34.66666666666667</v>
+        <v>41.33333333333334</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -2128,26 +2128,26 @@
         <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -2161,26 +2161,26 @@
         <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>32.66666666666666</v>
+        <v>38</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>32</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -2227,26 +2227,26 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>30.66666666666666</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -2260,26 +2260,26 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>30</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -2293,26 +2293,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>32</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -2326,26 +2326,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>31.33333333333334</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -2359,26 +2359,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>28</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -2392,26 +2392,26 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -2425,26 +2425,26 @@
         <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>27.33333333333333</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,26 +2458,26 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>26</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>26</v>
+        <v>25.33333333333334</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>26</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60">
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>20.66666666666667</v>
+        <v>20</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62">
@@ -2632,50 +2632,50 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="C63" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G63" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="I63" s="11" t="n">
         <v>123</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>24</v>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F63" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G63" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H63" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I63" s="11" t="n">
-        <v>126</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>15.33333333333333</v>
+        <v>17.33333333333334</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>15.33333333333333</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C66" s="17" t="n">
         <v>97</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2755,26 +2755,26 @@
         <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>12.66666666666667</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,26 +2788,26 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>12</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>7.333333333333333</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69">
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C69" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
         <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>2</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70">
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         <v>150</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>-0.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="17" t="n">
-        <v>1255</v>
+        <v>1316</v>
       </c>
       <c r="C74" s="17" t="n">
-        <v>810</v>
+        <v>836</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>1000</v>
       </c>
       <c r="H74" s="19" t="n">
-        <v>44.5</v>
+        <v>48</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>555</v>
+        <v>520</v>
       </c>
     </row>
     <row r="75">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>300</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>124</v>
+        <v>125.3333333333333</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>300</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>34</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         <v>300</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>89.33333333333333</v>
+        <v>92.66666666666666</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         <v>300</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>87.66666666666667</v>
+        <v>87.33333333333333</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>49</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         <v>300</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="B81" s="13" t="n">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="C81" s="13" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         <v>300</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>76.66666666666667</v>
+        <v>78</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82">
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C82" s="13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
@@ -3283,10 +3283,10 @@
         <v>300</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>67</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C83" s="13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3316,43 +3316,43 @@
         <v>300</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>53</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="inlineStr">
+      <c r="A84" s="12" t="inlineStr">
         <is>
           <t>Indupalli S.O</t>
         </is>
       </c>
-      <c r="B84" s="17" t="n">
-        <v>275</v>
-      </c>
-      <c r="C84" s="17" t="n">
-        <v>127</v>
-      </c>
-      <c r="D84" s="18" t="n">
-        <v>148</v>
-      </c>
-      <c r="E84" s="16" t="inlineStr">
+      <c r="B84" s="13" t="n">
+        <v>292</v>
+      </c>
+      <c r="C84" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="D84" s="14" t="n">
+        <v>163</v>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F84" s="17" t="n">
+      <c r="F84" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G84" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="H84" s="19" t="n">
-        <v>49.33333333333334</v>
+      <c r="G84" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="H84" s="15" t="n">
+        <v>54.33333333333334</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="B85" s="17" t="n">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C85" s="17" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         <v>300</v>
       </c>
       <c r="H85" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>49</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C86" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         <v>300</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>44.66666666666666</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C87" s="17" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>300</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C88" s="17" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         <v>300</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89">
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>300</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>21</v>
+        <v>25.33333333333334</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -3604,10 +3604,10 @@
         <v>309</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>131.3333333333333</v>
+        <v>130.6666666666667</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3637,10 +3637,10 @@
         <v>252</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,59 +3654,59 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Koyyagurapadu B.O</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Vinnakota B.O</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>182</v>
       </c>
-      <c r="C4" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>148</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>98.66666666666667</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>2</v>
+      <c r="C4" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>105.3333333333333</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -3720,26 +3720,26 @@
         <v>150</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>94</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -3753,26 +3753,26 @@
         <v>150</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>93.33333333333333</v>
+        <v>92.66666666666666</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -3786,10 +3786,10 @@
         <v>150</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>92.66666666666666</v>
+        <v>91.33333333333333</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>64</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>150</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>83.33333333333334</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -3865,13 +3865,13 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>25</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3885,92 +3885,92 @@
         <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>81.33333333333333</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>188</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Pedapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>134</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>116</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>77.33333333333333</v>
+      <c r="B12" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>81.33333333333333</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>150</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>76.66666666666667</v>
+        <v>78.66666666666666</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -4000,10 +4000,10 @@
         <v>126</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -4017,26 +4017,26 @@
         <v>150</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>76</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -4050,26 +4050,26 @@
         <v>150</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>73.33333333333333</v>
+        <v>74</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -4083,26 +4083,26 @@
         <v>150</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>72</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -4116,26 +4116,26 @@
         <v>150</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -4149,26 +4149,26 @@
         <v>150</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -4182,26 +4182,26 @@
         <v>150</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>70.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -4215,26 +4215,26 @@
         <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>68</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -4248,26 +4248,26 @@
         <v>150</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>66.66666666666666</v>
+        <v>70</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -4281,26 +4281,26 @@
         <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>66.66666666666666</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,26 +4314,26 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>66.66666666666666</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,26 +4347,26 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>66</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,26 +4380,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>66</v>
+        <v>64.66666666666666</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>60.66666666666667</v>
+        <v>62</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -4459,13 +4459,13 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>23</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,10 +4545,10 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31">
@@ -4558,13 +4558,13 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>44</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,158 +4578,158 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
+          <t>Nandivada B.O</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>55.33333333333334</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Dondapadu B.O</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>52.66666666666666</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Pedaparupudi B.O</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
           <t>Tenneru B.O</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
+      <c r="B35" s="13" t="n">
         <v>246</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C35" s="13" t="n">
         <v>171</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D35" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H32" s="15" t="n">
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I32" s="11" t="n">
+      <c r="I35" s="11" t="n">
         <v>75</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Unikili B.O</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="n">
-        <v>90</v>
-      </c>
-      <c r="C33" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G33" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H33" s="19" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>Komaravolu B.O</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="n">
-        <v>158</v>
-      </c>
-      <c r="C34" s="17" t="n">
-        <v>85</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G34" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H34" s="19" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Ponukumadu B.O</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="n">
-        <v>94</v>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C36" s="17" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
@@ -4743,26 +4743,26 @@
         <v>150</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>46.66666666666666</v>
+        <v>49.33333333333334</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="C37" s="17" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
@@ -4776,26 +4776,26 @@
         <v>150</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>44</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C38" s="17" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
         <v>150</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C39" s="17" t="n">
         <v>31</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -4842,26 +4842,26 @@
         <v>150</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>42.66666666666667</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -4875,26 +4875,26 @@
         <v>150</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>42</v>
+        <v>44.66666666666666</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
@@ -4908,26 +4908,26 @@
         <v>150</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>40.66666666666666</v>
+        <v>44</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -4941,59 +4941,59 @@
         <v>150</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>42</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="I43" s="11" t="n">
         <v>87</v>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>58</v>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>38.66666666666666</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -5007,26 +5007,26 @@
         <v>150</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>36.66666666666666</v>
+        <v>42</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C45" s="17" t="n">
         <v>36</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -5040,26 +5040,26 @@
         <v>150</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>42</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -5073,26 +5073,26 @@
         <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>34.66666666666667</v>
+        <v>41.33333333333334</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -5106,26 +5106,26 @@
         <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -5139,26 +5139,26 @@
         <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>32.66666666666666</v>
+        <v>38</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -5172,26 +5172,26 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>32</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -5205,26 +5205,26 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>30.66666666666666</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>30</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
@@ -5251,13 +5251,13 @@
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -5271,26 +5271,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>32</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -5304,26 +5304,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>31.33333333333334</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -5337,26 +5337,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>28</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -5370,26 +5370,26 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -5403,26 +5403,26 @@
         <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>27.33333333333333</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,26 +5436,26 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>26</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,26 +5469,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>26</v>
+        <v>25.33333333333334</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,10 +5502,10 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>26</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60">
@@ -5548,13 +5548,13 @@
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>20.66666666666667</v>
+        <v>20</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62">
@@ -5610,50 +5610,50 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="C63" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G63" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="I63" s="11" t="n">
         <v>123</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>24</v>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F63" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G63" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H63" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I63" s="11" t="n">
-        <v>126</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>15.33333333333333</v>
+        <v>17.33333333333334</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,10 +5700,10 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>15.33333333333333</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66">
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C66" s="17" t="n">
         <v>97</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5733,26 +5733,26 @@
         <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>12.66666666666667</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,26 +5766,26 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>12</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>7.333333333333333</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C69" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
         <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>2</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70">
@@ -5845,13 +5845,13 @@
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
         <v>150</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>-0.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71">
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>124</v>
+        <v>125.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6084,13 +6084,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6150,13 +6150,13 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>34</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>300</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>89.33333333333333</v>
+        <v>92.66666666666666</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -6183,13 +6183,13 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6203,10 +6203,10 @@
         <v>300</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>87.66666666666667</v>
+        <v>87.33333333333333</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>49</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         <v>300</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -6269,10 +6269,10 @@
         <v>300</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>76.66666666666667</v>
+        <v>78</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -6302,10 +6302,10 @@
         <v>300</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>67</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6335,43 +6335,43 @@
         <v>300</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>53</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Indupalli S.O</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
-        <v>275</v>
-      </c>
-      <c r="C11" s="17" t="n">
-        <v>127</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>148</v>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="n">
+        <v>292</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>163</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G11" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>49.33333333333334</v>
+      <c r="G11" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>54.33333333333334</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         <v>300</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>49</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>300</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>44.66666666666666</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         <v>300</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
@@ -6480,13 +6480,13 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
         <v>300</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16">
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>300</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>21</v>
+        <v>25.33333333333334</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>1255</v>
+        <v>1316</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>810</v>
+        <v>836</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>1000</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>44.5</v>
+        <v>48</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>555</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -6730,10 +6730,10 @@
         <v>309</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>131.3333333333333</v>
+        <v>130.6666666666667</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6763,10 +6763,10 @@
         <v>252</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6789,17 +6789,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>182</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6813,26 +6813,26 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>98.66666666666667</v>
+        <v>105.3333333333333</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,26 +6846,26 @@
         <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>94</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6879,10 +6879,10 @@
         <v>150</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>93.33333333333333</v>
+        <v>92.66666666666666</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -7065,13 +7065,13 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
@@ -7085,10 +7085,10 @@
         <v>150</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>-0.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
@@ -7098,13 +7098,13 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         <v>150</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>2</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>124</v>
+        <v>125.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>300</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>21</v>
+        <v>25.33333333333334</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         <v>300</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4">
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         <v>300</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>13746</v>
+        <v>14274</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5058</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>8688</v>
+        <v>9026</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -716,52 +716,52 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Bhushanagulla B.O</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>164</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>97.33333333333334</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>4</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bollapadu B.O</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         <v>150</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>92.66666666666666</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -808,26 +808,26 @@
         <v>150</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>91.33333333333333</v>
+        <v>92.66666666666666</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -841,26 +841,26 @@
         <v>150</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>88.66666666666667</v>
+        <v>91.33333333333333</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -874,26 +874,26 @@
         <v>150</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>88.66666666666667</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -907,26 +907,26 @@
         <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>83.33333333333334</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -940,92 +940,92 @@
         <v>150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>82</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B13" s="8" t="n">
         <v>191</v>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>122</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>81.33333333333333</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Pedapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>137</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>78.66666666666666</v>
+      <c r="C13" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>80.66666666666666</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -1039,26 +1039,26 @@
         <v>150</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>75.33333333333333</v>
+        <v>78.66666666666666</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -1072,26 +1072,26 @@
         <v>150</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -1105,26 +1105,26 @@
         <v>150</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>72.66666666666667</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -1138,26 +1138,26 @@
         <v>150</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -1171,23 +1171,23 @@
         <v>150</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>108</v>
@@ -1213,17 +1213,17 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1237,26 +1237,26 @@
         <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>70.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1270,26 +1270,26 @@
         <v>150</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1303,26 +1303,26 @@
         <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>67.33333333333333</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,23 +1336,23 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>98</v>
@@ -1378,17 +1378,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>64.66666666666666</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>64</v>
+        <v>64.66666666666666</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,23 +1501,23 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>59.33333333333334</v>
+        <v>62</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>89</v>
@@ -1543,17 +1543,17 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>16</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>57.33333333333334</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C38" s="17" t="n">
         <v>7</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         <v>150</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>48</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
@@ -1939,17 +1939,17 @@
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -1963,26 +1963,26 @@
         <v>150</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>42</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -1996,23 +1996,23 @@
         <v>150</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>42</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D44" s="18" t="n">
         <v>63</v>
@@ -2137,17 +2137,17 @@
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -2161,26 +2161,26 @@
         <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>38</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>38</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -2227,23 +2227,23 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>34</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D51" s="18" t="n">
         <v>50</v>
@@ -2269,17 +2269,17 @@
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -2293,26 +2293,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>32</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -2326,26 +2326,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>31.33333333333334</v>
+        <v>32</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>30.66666666666666</v>
+        <v>31.33333333333334</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55">
@@ -2434,17 +2434,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,27 +2458,27 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>26.66666666666667</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C58" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="D58" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="D58" s="18" t="n">
-        <v>38</v>
-      </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
           <t>BO</t>
@@ -2491,10 +2491,10 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>25.33333333333334</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59">
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C70" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         <v>150</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>2</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71">
@@ -2936,10 +2936,10 @@
         <v>250</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         <v>150</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-5.333333333333334</v>
+        <v>-6</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="17" t="n">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C74" s="17" t="n">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>1000</v>
       </c>
       <c r="H74" s="19" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="75">
@@ -3035,10 +3035,10 @@
         <v>440</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>300</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>125.3333333333333</v>
+        <v>125</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>34</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         <v>300</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>92.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="B81" s="13" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C81" s="13" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>234</v>
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C83" s="13" t="n">
         <v>52</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         <v>300</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>55.00000000000001</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="B85" s="17" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C85" s="17" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         <v>300</v>
       </c>
       <c r="H85" s="19" t="n">
-        <v>49</v>
+        <v>49.33333333333334</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86">
@@ -3497,10 +3497,10 @@
         <v>135</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>300</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>25.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3694,52 +3694,52 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Bhushanagulla B.O</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>164</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>97.33333333333334</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>4</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bollapadu B.O</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -3753,26 +3753,26 @@
         <v>150</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>92.66666666666666</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -3786,26 +3786,26 @@
         <v>150</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>91.33333333333333</v>
+        <v>92.66666666666666</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -3819,26 +3819,26 @@
         <v>150</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>88.66666666666667</v>
+        <v>91.33333333333333</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3852,26 +3852,26 @@
         <v>150</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>88.66666666666667</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3885,26 +3885,26 @@
         <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>83.33333333333334</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3918,92 +3918,92 @@
         <v>150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>82</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B13" s="8" t="n">
         <v>191</v>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>122</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>81.33333333333333</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Pedapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>137</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>78.66666666666666</v>
+      <c r="C13" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>80.66666666666666</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -4017,26 +4017,26 @@
         <v>150</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>75.33333333333333</v>
+        <v>78.66666666666666</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -4050,26 +4050,26 @@
         <v>150</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -4083,59 +4083,59 @@
         <v>150</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>72.66666666666667</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C17" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>74</v>
+      </c>
+      <c r="I17" s="11" t="n">
         <v>39</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>108</v>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>72</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -4149,23 +4149,23 @@
         <v>150</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>108</v>
@@ -4191,17 +4191,17 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -4215,26 +4215,26 @@
         <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>70.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -4248,26 +4248,26 @@
         <v>150</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -4281,26 +4281,26 @@
         <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>67.33333333333333</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -4356,17 +4356,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,26 +4380,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>64.66666666666666</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>64</v>
+        <v>64.66666666666666</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,26 +4446,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>59.33333333333334</v>
+        <v>62</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
@@ -4521,17 +4521,17 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32">
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>16</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>57.33333333333334</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C38" s="17" t="n">
         <v>7</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
         <v>150</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>48</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
@@ -4917,17 +4917,17 @@
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -4941,26 +4941,26 @@
         <v>150</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>42</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -4974,10 +4974,10 @@
         <v>150</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>42</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44">
@@ -5115,17 +5115,17 @@
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -5139,26 +5139,26 @@
         <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>38</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -5172,26 +5172,26 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>38</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -5205,23 +5205,23 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>34</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D51" s="18" t="n">
         <v>50</v>
@@ -5247,17 +5247,17 @@
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -5271,26 +5271,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>32</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -5304,26 +5304,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>31.33333333333334</v>
+        <v>32</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>30.66666666666666</v>
+        <v>31.33333333333334</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55">
@@ -5379,14 +5379,14 @@
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>44</v>
@@ -5412,17 +5412,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,27 +5436,27 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>26.66666666666667</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C58" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="D58" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="D58" s="18" t="n">
-        <v>38</v>
-      </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
           <t>BO</t>
@@ -5469,10 +5469,10 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>25.33333333333334</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59">
@@ -5845,13 +5845,13 @@
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C70" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
         <v>150</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>2</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71">
@@ -5914,10 +5914,10 @@
         <v>250</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         <v>150</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-5.333333333333334</v>
+        <v>-6</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73">
@@ -6054,10 +6054,10 @@
         <v>440</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>125.3333333333333</v>
+        <v>125</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6150,13 +6150,13 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>34</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>300</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>92.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -6249,10 +6249,10 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>234</v>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>52</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         <v>300</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>55.00000000000001</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         <v>300</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>49</v>
+        <v>49.33333333333334</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6516,10 +6516,10 @@
         <v>135</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>300</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>25.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>1000</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -6822,17 +6822,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,26 +6846,26 @@
         <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>97.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6879,10 +6879,10 @@
         <v>150</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>92.66666666666666</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7002,10 +7002,10 @@
         <v>250</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7019,10 +7019,10 @@
         <v>150</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>-5.333333333333334</v>
+        <v>-6</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4">
@@ -7065,13 +7065,13 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
@@ -7085,10 +7085,10 @@
         <v>150</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>2</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
@@ -7208,10 +7208,10 @@
         <v>440</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>125.3333333333333</v>
+        <v>125</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7381,10 +7381,10 @@
         <v>135</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>300</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>25.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>14274</v>
+        <v>14404</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5248</v>
+        <v>5261</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>9026</v>
+        <v>9143</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>130.6666666666667</v>
+        <v>140</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -652,17 +652,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>128</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -685,17 +685,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>105.3333333333333</v>
+        <v>128</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -718,17 +718,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -742,125 +742,125 @@
         <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bollapadu B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>164</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>109.3333333333333</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Bhushanagulla B.O</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>164</v>
-      </c>
-      <c r="C6" s="8" t="n">
+      <c r="B7" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>97.33333333333334</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Dosapadu B.O</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>168</v>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="B8" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>139</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>92.66666666666666</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Koyyagurapadu B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>182</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>137</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>91.33333333333333</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>13</v>
+      <c r="D8" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>101.3333333333333</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -874,26 +874,26 @@
         <v>150</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>88.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -907,26 +907,26 @@
         <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>91.33333333333333</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -940,26 +940,26 @@
         <v>150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>88.66666666666667</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,158 +973,158 @@
         <v>150</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>82</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>Moparru B.O</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Guruvindagunta B.O</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="D13" s="9" t="n">
+      <c r="B16" s="8" t="n">
+        <v>192</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H13" s="10" t="n">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H16" s="10" t="n">
         <v>80.66666666666666</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="I16" s="11" t="n">
         <v>29</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Pedapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>137</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>78.66666666666666</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Moparru B.O</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>114</v>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>76</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Guruvindagunta B.O</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>126</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>113</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>75.33333333333333</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -1138,26 +1138,26 @@
         <v>150</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>74</v>
+        <v>78.66666666666666</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
         <v>150</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1204,26 +1204,26 @@
         <v>150</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>72</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1237,23 +1237,23 @@
         <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>108</v>
@@ -1279,17 +1279,17 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1303,26 +1303,26 @@
         <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>70.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,26 +1336,26 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>67.33333333333333</v>
+        <v>71.33333333333334</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,27 +1369,27 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="C25" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>98</v>
-      </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
           <t>BO</t>
@@ -1402,26 +1402,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>64.66666666666666</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>64</v>
+        <v>64.66666666666666</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>59.33333333333334</v>
+        <v>62</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>59.33333333333334</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,26 +1600,26 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1633,26 +1633,26 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>57.33333333333334</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,26 +1666,26 @@
         <v>150</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
         <v>150</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>52</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35">
@@ -1741,14 +1741,14 @@
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" s="17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D36" s="18" t="n">
         <v>74</v>
@@ -1774,17 +1774,17 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="C37" s="17" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
@@ -1798,26 +1798,26 @@
         <v>150</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>48.66666666666667</v>
+        <v>49.33333333333334</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C38" s="17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
         <v>150</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>48</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -1864,26 +1864,26 @@
         <v>150</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>45.33333333333333</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -1897,26 +1897,26 @@
         <v>150</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>44.66666666666666</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
@@ -1930,26 +1930,26 @@
         <v>150</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>44</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
         <v>150</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
         <v>150</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>42.66666666666667</v>
+        <v>44</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -2029,10 +2029,10 @@
         <v>150</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>42</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -2062,26 +2062,26 @@
         <v>150</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>42</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -2095,26 +2095,26 @@
         <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>41.33333333333334</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>42</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48">
@@ -2203,17 +2203,17 @@
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -2227,26 +2227,26 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -2260,26 +2260,26 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -2293,26 +2293,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -2326,26 +2326,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>32</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -2359,26 +2359,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>31.33333333333334</v>
+        <v>32</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>30</v>
+        <v>31.33333333333334</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56">
@@ -2434,14 +2434,14 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D57" s="18" t="n">
         <v>44</v>
@@ -2467,17 +2467,17 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>26.66666666666667</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,26 +2524,26 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>24.66666666666667</v>
+        <v>28</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -2557,26 +2557,26 @@
         <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>22</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62">
@@ -2632,17 +2632,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -2656,26 +2656,26 @@
         <v>150</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>18</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>17.33333333333334</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,26 +2722,26 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>16.66666666666666</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2755,26 +2755,26 @@
         <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>15.33333333333333</v>
+        <v>18</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,26 +2788,26 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>14.66666666666667</v>
+        <v>17.33333333333334</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>11.33333333333333</v>
+        <v>16</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69">
@@ -2834,30 +2834,30 @@
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C69" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G69" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H69" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D69" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F69" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G69" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H69" s="19" t="n">
-        <v>9.333333333333334</v>
-      </c>
       <c r="I69" s="11" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70">
@@ -2900,13 +2900,13 @@
         </is>
       </c>
       <c r="B71" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C71" s="17" t="n">
         <v>11</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -2920,26 +2920,26 @@
         <v>150</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>-4</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -2953,26 +2953,26 @@
         <v>150</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>92</v>
+        <v>250</v>
       </c>
       <c r="C73" s="17" t="n">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-29</v>
+        <v>-9</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         <v>150</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-19.33333333333333</v>
+        <v>-6</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="17" t="n">
-        <v>1319</v>
+        <v>1388</v>
       </c>
       <c r="C74" s="17" t="n">
-        <v>838</v>
+        <v>891</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>1000</v>
       </c>
       <c r="H74" s="19" t="n">
-        <v>48.1</v>
+        <v>49.7</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
     </row>
     <row r="75">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>300</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>300</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>113</v>
+        <v>115.3333333333333</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3098,13 +3098,13 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>300</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>103.3333333333333</v>
+        <v>105.3333333333333</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C78" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         <v>300</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>96</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         <v>300</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>87.33333333333333</v>
+        <v>89</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,43 +3217,43 @@
         <v>300</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>Mudinepalli S.O</t>
         </is>
       </c>
-      <c r="B81" s="13" t="n">
-        <v>501</v>
-      </c>
-      <c r="C81" s="13" t="n">
-        <v>267</v>
-      </c>
-      <c r="D81" s="14" t="n">
-        <v>234</v>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="B81" s="8" t="n">
+        <v>521</v>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>245</v>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F81" s="13" t="n">
+      <c r="F81" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G81" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="H81" s="15" t="n">
-        <v>78</v>
+      <c r="G81" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="H81" s="10" t="n">
+        <v>81.66666666666667</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82">
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C82" s="13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
@@ -3283,26 +3283,26 @@
         <v>300</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>Manikonda S.O</t>
+          <t>Indupalli S.O</t>
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="C83" s="13" t="n">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3316,26 +3316,26 @@
         <v>300</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>64.66666666666666</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>Indupalli S.O</t>
+          <t>Manikonda S.O</t>
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
@@ -3349,43 +3349,43 @@
         <v>300</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>54.33333333333334</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="A85" s="12" t="inlineStr">
         <is>
           <t>Rajendranagar Colony S.O</t>
         </is>
       </c>
-      <c r="B85" s="17" t="n">
-        <v>372</v>
-      </c>
-      <c r="C85" s="17" t="n">
-        <v>224</v>
-      </c>
-      <c r="D85" s="18" t="n">
-        <v>148</v>
-      </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="B85" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="C85" s="13" t="n">
+        <v>232</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>153</v>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F85" s="17" t="n">
+      <c r="F85" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G85" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="H85" s="19" t="n">
-        <v>49.33333333333334</v>
+      <c r="G85" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="H85" s="15" t="n">
+        <v>51</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C86" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         <v>300</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>44.66666666666666</v>
+        <v>45</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C87" s="17" t="n">
         <v>58</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>300</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>39.66666666666666</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C88" s="17" t="n">
         <v>90</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         <v>300</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>38</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89">
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>300</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>25</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>130.6666666666667</v>
+        <v>140</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3630,17 +3630,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>128</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3663,17 +3663,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>105.3333333333333</v>
+        <v>128</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -3696,17 +3696,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -3720,125 +3720,125 @@
         <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bollapadu B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>164</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>109.3333333333333</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Bhushanagulla B.O</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>164</v>
-      </c>
-      <c r="C6" s="8" t="n">
+      <c r="B7" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>97.33333333333334</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Dosapadu B.O</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>168</v>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="B8" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>139</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>92.66666666666666</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Koyyagurapadu B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>182</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>137</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>91.33333333333333</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>13</v>
+      <c r="D8" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>101.3333333333333</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3852,26 +3852,26 @@
         <v>150</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>88.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3885,26 +3885,26 @@
         <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>91.33333333333333</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3918,26 +3918,26 @@
         <v>150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>88.66666666666667</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,158 +3951,158 @@
         <v>150</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>82</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>Moparru B.O</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Guruvindagunta B.O</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="D13" s="9" t="n">
+      <c r="B16" s="8" t="n">
+        <v>192</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H13" s="10" t="n">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H16" s="10" t="n">
         <v>80.66666666666666</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="I16" s="11" t="n">
         <v>29</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Pedapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>137</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>78.66666666666666</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Moparru B.O</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>114</v>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>76</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Guruvindagunta B.O</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>126</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>113</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>75.33333333333333</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -4116,26 +4116,26 @@
         <v>150</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>74</v>
+        <v>78.66666666666666</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -4149,26 +4149,26 @@
         <v>150</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -4182,26 +4182,26 @@
         <v>150</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>72</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -4215,23 +4215,23 @@
         <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>108</v>
@@ -4257,17 +4257,17 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -4281,26 +4281,26 @@
         <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>70.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,26 +4314,26 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>67.33333333333333</v>
+        <v>71.33333333333334</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,26 +4347,26 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,26 +4380,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>64.66666666666666</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,26 +4446,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>64</v>
+        <v>64.66666666666666</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,26 +4479,26 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>59.33333333333334</v>
+        <v>62</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>59.33333333333334</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,26 +4578,26 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4611,26 +4611,26 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>57.33333333333334</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,26 +4644,26 @@
         <v>150</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -4677,10 +4677,10 @@
         <v>150</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>52</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35">
@@ -4719,14 +4719,14 @@
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C36" s="17" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D36" s="18" t="n">
         <v>74</v>
@@ -4752,17 +4752,17 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="C37" s="17" t="n">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
@@ -4776,26 +4776,26 @@
         <v>150</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>48.66666666666667</v>
+        <v>49.33333333333334</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C38" s="17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
         <v>150</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>48</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39">
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C39" s="17" t="n">
         <v>31</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -4842,26 +4842,26 @@
         <v>150</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>45.33333333333333</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -4875,26 +4875,26 @@
         <v>150</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>44.66666666666666</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
@@ -4908,26 +4908,26 @@
         <v>150</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>44</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         <v>150</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
@@ -4954,13 +4954,13 @@
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -4974,26 +4974,26 @@
         <v>150</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>42.66666666666667</v>
+        <v>44</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -5007,26 +5007,26 @@
         <v>150</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>42</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -5040,26 +5040,26 @@
         <v>150</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>42</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -5073,26 +5073,26 @@
         <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>41.33333333333334</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>42</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48">
@@ -5148,14 +5148,14 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D49" s="18" t="n">
         <v>57</v>
@@ -5181,17 +5181,17 @@
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -5205,26 +5205,26 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -5238,26 +5238,26 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -5271,26 +5271,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>33.33333333333333</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -5304,26 +5304,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>32</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -5337,26 +5337,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>31.33333333333334</v>
+        <v>32</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -5370,23 +5370,23 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>30</v>
+        <v>31.33333333333334</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>44</v>
@@ -5412,14 +5412,14 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D57" s="18" t="n">
         <v>44</v>
@@ -5445,17 +5445,17 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,26 +5469,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>26.66666666666667</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>24.66666666666667</v>
+        <v>28</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -5535,26 +5535,26 @@
         <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>22</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62">
@@ -5610,17 +5610,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -5634,26 +5634,26 @@
         <v>150</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>18</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>17.33333333333334</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,26 +5700,26 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>16.66666666666666</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5733,26 +5733,26 @@
         <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>15.33333333333333</v>
+        <v>18</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,26 +5766,26 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>14.66666666666667</v>
+        <v>17.33333333333334</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>11.33333333333333</v>
+        <v>16</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69">
@@ -5812,30 +5812,30 @@
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C69" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G69" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H69" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D69" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F69" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G69" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H69" s="19" t="n">
-        <v>9.333333333333334</v>
-      </c>
       <c r="I69" s="11" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70">
@@ -5878,13 +5878,13 @@
         </is>
       </c>
       <c r="B71" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C71" s="17" t="n">
         <v>11</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -5898,26 +5898,26 @@
         <v>150</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>-4</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -5931,26 +5931,26 @@
         <v>150</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>92</v>
+        <v>250</v>
       </c>
       <c r="C73" s="17" t="n">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-29</v>
+        <v>-9</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -5964,10 +5964,10 @@
         <v>150</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-19.33333333333333</v>
+        <v>-6</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6084,13 +6084,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>113</v>
+        <v>115.3333333333333</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>300</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>103.3333333333333</v>
+        <v>105.3333333333333</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6150,13 +6150,13 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>300</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>96</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -6183,13 +6183,13 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6203,10 +6203,10 @@
         <v>300</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>87.33333333333333</v>
+        <v>89</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,43 +6236,43 @@
         <v>300</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Mudinepalli S.O</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>501</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>267</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>234</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="B8" s="8" t="n">
+        <v>521</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>245</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G8" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>78</v>
+      <c r="G8" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>81.66666666666667</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -6302,26 +6302,26 @@
         <v>300</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Manikonda S.O</t>
+          <t>Indupalli S.O</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6335,26 +6335,26 @@
         <v>300</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>64.66666666666666</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Indupalli S.O</t>
+          <t>Manikonda S.O</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6368,43 +6368,43 @@
         <v>300</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>54.33333333333334</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Rajendranagar Colony S.O</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>372</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>224</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>148</v>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="B12" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>232</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>153</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G12" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>49.33333333333334</v>
+      <c r="G12" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>51</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>300</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>44.66666666666666</v>
+        <v>45</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C14" s="17" t="n">
         <v>58</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         <v>300</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>39.66666666666666</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
@@ -6480,13 +6480,13 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C15" s="17" t="n">
         <v>90</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
         <v>300</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>38</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>300</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>25</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>1319</v>
+        <v>1388</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>838</v>
+        <v>891</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>1000</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>48.1</v>
+        <v>49.7</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>130.6666666666667</v>
+        <v>140</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6756,17 +6756,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>128</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6789,17 +6789,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>105.3333333333333</v>
+        <v>128</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6822,17 +6822,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -6855,18 +6855,18 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>164</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>146</v>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>BO</t>
@@ -6879,10 +6879,10 @@
         <v>150</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>97.33333333333334</v>
+        <v>109.3333333333333</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6962,17 +6962,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>92</v>
+        <v>250</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>-29</v>
+        <v>-9</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6986,26 +6986,26 @@
         <v>150</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>-19.33333333333333</v>
+        <v>-6</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7019,10 +7019,10 @@
         <v>150</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
@@ -7032,13 +7032,13 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="17" t="n">
         <v>11</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7052,10 +7052,10 @@
         <v>150</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>-4</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
@@ -7098,30 +7098,30 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H6" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D6" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>9.333333333333334</v>
-      </c>
       <c r="I6" s="11" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>113</v>
+        <v>115.3333333333333</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7271,13 +7271,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>300</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>103.3333333333333</v>
+        <v>105.3333333333333</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>300</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>25</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C3" s="17" t="n">
         <v>90</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         <v>300</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>38</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4">
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C4" s="17" t="n">
         <v>58</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         <v>300</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>39.66666666666666</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>14404</v>
+        <v>15087</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5261</v>
+        <v>5474</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>9143</v>
+        <v>9613</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>115</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>140</v>
+        <v>146.6666666666667</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -656,13 +656,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>44</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>128.6666666666667</v>
+        <v>130</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>60</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>128</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>112</v>
+        <v>111.3333333333333</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -751,14 +751,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>164</v>
@@ -784,17 +784,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>150</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>104</v>
+        <v>109.3333333333333</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -817,17 +817,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -841,43 +841,43 @@
         <v>150</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>101.3333333333333</v>
+        <v>104</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>211</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>144</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>96</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>6</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Dosapadu B.O</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>101.3333333333333</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -907,26 +907,26 @@
         <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>91.33333333333333</v>
+        <v>98.66666666666667</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -940,26 +940,26 @@
         <v>150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>88.66666666666667</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
         <v>150</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>91.33333333333333</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>19</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         <v>150</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>84</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1039,26 +1039,26 @@
         <v>150</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>81.33333333333333</v>
+        <v>88</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>141</v>
+        <v>228</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1072,158 +1072,158 @@
         <v>150</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>81.33333333333333</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>Kanukollu B.O</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>178</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Lingavaram B.O</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>144</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>82.66666666666667</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>192</v>
-      </c>
-      <c r="C16" s="8" t="n">
+      <c r="B18" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>80.66666666666666</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Tativarru B.O</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>146</v>
-      </c>
-      <c r="C17" s="13" t="n">
+      <c r="D18" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="I19" s="11" t="n">
         <v>28</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>78.66666666666666</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Gunnanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>141</v>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Lingavaram B.O</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>113</v>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>75.33333333333333</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1237,26 +1237,26 @@
         <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>74</v>
+        <v>79.33333333333333</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1270,26 +1270,26 @@
         <v>150</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1303,26 +1303,26 @@
         <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>72</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,26 +1336,26 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,26 +1369,26 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>67.33333333333333</v>
+        <v>71.33333333333334</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>40</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>66.66666666666666</v>
+        <v>71.33333333333334</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>68</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>64.66666666666666</v>
+        <v>68</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>64</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>56.66666666666666</v>
+        <v>64</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,26 +1600,26 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>56.66666666666666</v>
+        <v>63.33333333333333</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1633,26 +1633,26 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,26 +1666,26 @@
         <v>150</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -1699,356 +1699,356 @@
         <v>150</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>246</v>
+        <v>106</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="D35" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Ingilipakalanka B.O</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Chinaparupudi B.O</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>144</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>55.33333333333334</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Pedaparupudi B.O</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>55.33333333333334</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Lankapalli Agraharam B.O</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Nandivada B.O</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Koduru B.O</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>52.66666666666666</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Nuzella B.O</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>138</v>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>50.66666666666667</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H35" s="15" t="n">
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H43" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="I43" s="11" t="n">
         <v>75</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Guntakoduru B.O</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="n">
-        <v>95</v>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G36" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H36" s="19" t="n">
-        <v>49.33333333333334</v>
-      </c>
-      <c r="I36" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="n">
-        <v>81</v>
-      </c>
-      <c r="C37" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G37" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>49.33333333333334</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>Lankapalli Agraharam B.O</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="n">
-        <v>86</v>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>Dondapadu B.O</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="n">
-        <v>118</v>
-      </c>
-      <c r="C39" s="17" t="n">
-        <v>48</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G39" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>Pedakamanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="n">
-        <v>101</v>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G40" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Ponukumadu B.O</t>
         </is>
       </c>
-      <c r="B41" s="17" t="n">
-        <v>97</v>
-      </c>
-      <c r="C41" s="17" t="n">
+      <c r="B44" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="C44" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="D41" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G41" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>Chinaparupudi B.O</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="n">
-        <v>128</v>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>68</v>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G42" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>45.33333333333333</v>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>Nuzella B.O</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="n">
-        <v>128</v>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>62</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>66</v>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="n">
-        <v>74</v>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>65</v>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G44" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H44" s="19" t="n">
-        <v>43.33333333333334</v>
+      <c r="D44" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -2062,26 +2062,26 @@
         <v>150</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -2095,26 +2095,26 @@
         <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>42.66666666666667</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -2128,26 +2128,26 @@
         <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>42</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -2161,26 +2161,26 @@
         <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>46</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -2227,26 +2227,26 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -2260,26 +2260,26 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>37.33333333333334</v>
+        <v>44</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -2293,26 +2293,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>37.33333333333334</v>
+        <v>44</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -2326,26 +2326,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>32.66666666666666</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -2359,26 +2359,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>32</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -2392,26 +2392,26 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>31.33333333333334</v>
+        <v>42</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -2425,26 +2425,26 @@
         <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,26 +2458,26 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>38</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,26 +2524,26 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>28</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -2557,26 +2557,26 @@
         <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>23.33333333333333</v>
+        <v>36</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,26 +2590,26 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -2623,26 +2623,26 @@
         <v>150</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>19.33333333333333</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -2656,26 +2656,26 @@
         <v>150</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>34.66666666666667</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,26 +2722,26 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>22.66666666666666</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2755,26 +2755,26 @@
         <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>18</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,26 +2788,26 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>17.33333333333334</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2821,26 +2821,26 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>16</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -2854,92 +2854,92 @@
         <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>14</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Anamanapudi B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C70" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H70" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D70" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E70" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F70" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G70" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H70" s="19" t="n">
-        <v>3.333333333333333</v>
-      </c>
       <c r="I70" s="11" t="n">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Ilaparru B.O</t>
+          <t>Anamanapudi B.O</t>
         </is>
       </c>
       <c r="B71" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C71" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H71" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C71" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G71" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H71" s="19" t="n">
-        <v>-3.333333333333333</v>
-      </c>
       <c r="I71" s="11" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -2953,26 +2953,26 @@
         <v>150</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-4</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Ilaparru B.O</t>
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="C73" s="17" t="n">
-        <v>259</v>
+        <v>11</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -2986,43 +2986,43 @@
         <v>150</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-6</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B74" s="17" t="n">
-        <v>1388</v>
-      </c>
-      <c r="C74" s="17" t="n">
-        <v>891</v>
-      </c>
-      <c r="D74" s="18" t="n">
-        <v>497</v>
-      </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="B74" s="13" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C74" s="13" t="n">
+        <v>918</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>512</v>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F74" s="17" t="n">
+      <c r="F74" s="13" t="n">
         <v>2000</v>
       </c>
-      <c r="G74" s="17" t="n">
+      <c r="G74" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="H74" s="19" t="n">
-        <v>49.7</v>
+      <c r="H74" s="15" t="n">
+        <v>51.2</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>503</v>
+        <v>488</v>
       </c>
     </row>
     <row r="75">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>300</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>129</v>
+        <v>125.6666666666667</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>300</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>115.3333333333333</v>
+        <v>117.3333333333333</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3127,17 +3127,17 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Rudrapaka S.O</t>
+          <t>Moturu S.O</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="C78" s="8" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -3151,26 +3151,26 @@
         <v>300</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>97.66666666666667</v>
+        <v>99.33333333333333</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Mudunuru S.O</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -3184,26 +3184,26 @@
         <v>300</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>89</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Moturu S.O</t>
+          <t>Mudunuru S.O</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>310</v>
+        <v>367</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         <v>300</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>86</v>
+        <v>90.33333333333333</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         <v>300</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>81.66666666666667</v>
+        <v>83.66666666666667</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82">
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C82" s="13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
@@ -3283,10 +3283,10 @@
         <v>300</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>71</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="C83" s="13" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         <v>300</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>64.66666666666666</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C84" s="13" t="n">
         <v>56</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
@@ -3349,10 +3349,10 @@
         <v>300</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>58.33333333333334</v>
+        <v>59</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="B85" s="13" t="n">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C85" s="13" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         <v>300</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>51</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C86" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         <v>300</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="87">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C87" s="17" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>300</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>39.66666666666666</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C88" s="17" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         <v>300</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>38.33333333333334</v>
+        <v>34</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89">
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>300</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>28.66666666666667</v>
+        <v>33</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>115</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>140</v>
+        <v>146.6666666666667</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>44</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>128.6666666666667</v>
+        <v>130</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>60</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>128</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>112</v>
+        <v>111.3333333333333</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -3766,13 +3766,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>150</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>104</v>
+        <v>109.3333333333333</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -3795,17 +3795,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -3819,43 +3819,43 @@
         <v>150</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>101.3333333333333</v>
+        <v>104</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>211</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>144</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>96</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>6</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Dosapadu B.O</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>101.3333333333333</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3865,13 +3865,13 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3885,26 +3885,26 @@
         <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>91.33333333333333</v>
+        <v>98.66666666666667</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3918,26 +3918,26 @@
         <v>150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>88.66666666666667</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,26 +3951,26 @@
         <v>150</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>91.33333333333333</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>19</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3984,26 +3984,26 @@
         <v>150</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>84</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -4017,26 +4017,26 @@
         <v>150</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>81.33333333333333</v>
+        <v>88</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4050,158 +4050,158 @@
         <v>150</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>81.33333333333333</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>Kanukollu B.O</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>178</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Lingavaram B.O</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>144</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>82.66666666666667</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>192</v>
-      </c>
-      <c r="C16" s="8" t="n">
+      <c r="B18" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>80.66666666666666</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Tativarru B.O</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>146</v>
-      </c>
-      <c r="C17" s="13" t="n">
+      <c r="D18" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="I19" s="11" t="n">
         <v>28</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>78.66666666666666</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Gunnanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>141</v>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Lingavaram B.O</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>113</v>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>75.33333333333333</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -4215,26 +4215,26 @@
         <v>150</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>74</v>
+        <v>79.33333333333333</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -4248,26 +4248,26 @@
         <v>150</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -4281,26 +4281,26 @@
         <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>72</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,26 +4314,26 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,26 +4347,26 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>67.33333333333333</v>
+        <v>71.33333333333334</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>40</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,26 +4380,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>66.66666666666666</v>
+        <v>71.33333333333334</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>68</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,26 +4446,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>64.66666666666666</v>
+        <v>68</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,26 +4479,26 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>64</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>56.66666666666666</v>
+        <v>64</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,26 +4578,26 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>56.66666666666666</v>
+        <v>63.33333333333333</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4611,26 +4611,26 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,26 +4644,26 @@
         <v>150</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -4677,356 +4677,356 @@
         <v>150</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>246</v>
+        <v>106</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="D35" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Ingilipakalanka B.O</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Chinaparupudi B.O</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>144</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>55.33333333333334</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Pedaparupudi B.O</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>55.33333333333334</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Nandivada B.O</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Lankapalli Agraharam B.O</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Koduru B.O</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>52.66666666666666</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Nuzella B.O</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>138</v>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>50.66666666666667</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H35" s="15" t="n">
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H43" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="I43" s="11" t="n">
         <v>75</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="n">
-        <v>81</v>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G36" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H36" s="19" t="n">
-        <v>49.33333333333334</v>
-      </c>
-      <c r="I36" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Guntakoduru B.O</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="n">
-        <v>95</v>
-      </c>
-      <c r="C37" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G37" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>49.33333333333334</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>Lankapalli Agraharam B.O</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="n">
-        <v>86</v>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>Pedakamanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="n">
-        <v>101</v>
-      </c>
-      <c r="C39" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G39" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>Dondapadu B.O</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="n">
-        <v>118</v>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>48</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G40" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Ponukumadu B.O</t>
         </is>
       </c>
-      <c r="B41" s="17" t="n">
-        <v>97</v>
-      </c>
-      <c r="C41" s="17" t="n">
+      <c r="B44" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="C44" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="D41" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G41" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>Chinaparupudi B.O</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="n">
-        <v>128</v>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>68</v>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G42" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>45.33333333333333</v>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>Nuzella B.O</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="n">
-        <v>128</v>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>62</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>66</v>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="n">
-        <v>74</v>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>65</v>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G44" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H44" s="19" t="n">
-        <v>43.33333333333334</v>
+      <c r="D44" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -5040,26 +5040,26 @@
         <v>150</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -5073,26 +5073,26 @@
         <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>42.66666666666667</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -5106,26 +5106,26 @@
         <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>42</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -5139,26 +5139,26 @@
         <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>46</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -5172,26 +5172,26 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -5205,26 +5205,26 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -5238,26 +5238,26 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>37.33333333333334</v>
+        <v>44</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -5271,26 +5271,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>37.33333333333334</v>
+        <v>44</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -5304,26 +5304,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>32.66666666666666</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -5337,26 +5337,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>32</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -5370,26 +5370,26 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>31.33333333333334</v>
+        <v>42</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -5403,26 +5403,26 @@
         <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,26 +5436,26 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,26 +5469,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>29.33333333333333</v>
+        <v>38</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>28</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -5535,26 +5535,26 @@
         <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>23.33333333333333</v>
+        <v>36</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,26 +5568,26 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -5601,26 +5601,26 @@
         <v>150</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>19.33333333333333</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -5634,26 +5634,26 @@
         <v>150</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>34.66666666666667</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,26 +5700,26 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>22.66666666666666</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5733,26 +5733,26 @@
         <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>18</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,26 +5766,26 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>17.33333333333334</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5799,26 +5799,26 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>16</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5832,92 +5832,92 @@
         <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>14</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Anamanapudi B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C70" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H70" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D70" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E70" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F70" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G70" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H70" s="19" t="n">
-        <v>3.333333333333333</v>
-      </c>
       <c r="I70" s="11" t="n">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Ilaparru B.O</t>
+          <t>Anamanapudi B.O</t>
         </is>
       </c>
       <c r="B71" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C71" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H71" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C71" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G71" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H71" s="19" t="n">
-        <v>-3.333333333333333</v>
-      </c>
       <c r="I71" s="11" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -5931,26 +5931,26 @@
         <v>150</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-4</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Ilaparru B.O</t>
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="C73" s="17" t="n">
-        <v>259</v>
+        <v>11</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -5964,10 +5964,10 @@
         <v>150</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-6</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>129</v>
+        <v>125.6666666666667</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6084,13 +6084,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>115.3333333333333</v>
+        <v>117.3333333333333</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6146,17 +6146,17 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Rudrapaka S.O</t>
+          <t>Moturu S.O</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6170,26 +6170,26 @@
         <v>300</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>97.66666666666667</v>
+        <v>99.33333333333333</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Mudunuru S.O</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6203,26 +6203,26 @@
         <v>300</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>89</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Moturu S.O</t>
+          <t>Mudunuru S.O</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>310</v>
+        <v>367</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         <v>300</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>86</v>
+        <v>90.33333333333333</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6269,10 +6269,10 @@
         <v>300</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>81.66666666666667</v>
+        <v>83.66666666666667</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -6302,10 +6302,10 @@
         <v>300</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>71</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         <v>300</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>64.66666666666666</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -6348,13 +6348,13 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>56</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>300</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>58.33333333333334</v>
+        <v>59</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         <v>300</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>51</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>300</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         <v>300</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>39.66666666666666</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
@@ -6480,13 +6480,13 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
         <v>300</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>38.33333333333334</v>
+        <v>34</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>300</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>28.66666666666667</v>
+        <v>33</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -6614,36 +6614,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
-        <v>1388</v>
-      </c>
-      <c r="C2" s="17" t="n">
-        <v>891</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <v>497</v>
-      </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="B2" s="13" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>918</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>512</v>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="13" t="n">
         <v>2000</v>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="H2" s="19" t="n">
-        <v>49.7</v>
+      <c r="H2" s="15" t="n">
+        <v>51.2</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>503</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>115</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>140</v>
+        <v>146.6666666666667</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6760,13 +6760,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>44</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>128.6666666666667</v>
+        <v>130</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6793,13 +6793,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>60</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>128</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6826,13 +6826,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>112</v>
+        <v>111.3333333333333</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -6962,17 +6962,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Ilaparru B.O</t>
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>259</v>
+        <v>11</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6986,26 +6986,26 @@
         <v>150</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>-6</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7019,92 +7019,92 @@
         <v>150</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>-4</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Ilaparru B.O</t>
+          <t>Anamanapudi B.O</t>
         </is>
       </c>
       <c r="B4" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H4" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" s="18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>-3.333333333333333</v>
-      </c>
       <c r="I4" s="11" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Anamanapudi B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C5" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H5" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D5" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>3.333333333333333</v>
-      </c>
       <c r="I5" s="11" t="n">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         <v>150</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>14</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>129</v>
+        <v>125.6666666666667</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>115.3333333333333</v>
+        <v>117.3333333333333</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>300</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>28.66666666666667</v>
+        <v>33</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3">
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         <v>300</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>38.33333333333334</v>
+        <v>34</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         <v>300</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>39.66666666666666</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>15087</v>
+        <v>15966</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5474</v>
+        <v>5602</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>9613</v>
+        <v>10364</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -659,10 +659,10 @@
         <v>239</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>130</v>
+        <v>123.3333333333333</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -692,10 +692,10 @@
         <v>253</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>128.6666666666667</v>
+        <v>115.3333333333333</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -949,17 +949,17 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
         <v>150</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>91.33333333333333</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>153</v>
+        <v>238</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1006,59 +1006,59 @@
         <v>150</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="C14" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>90.66666666666666</v>
+      </c>
+      <c r="I14" s="11" t="n">
         <v>14</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>132</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1072,26 +1072,26 @@
         <v>150</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1105,26 +1105,26 @@
         <v>150</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1138,26 +1138,26 @@
         <v>150</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>82.66666666666667</v>
+        <v>84</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
         <v>150</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>82</v>
+        <v>82.66666666666667</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1204,43 +1204,43 @@
         <v>150</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>81.33333333333333</v>
+        <v>80.66666666666666</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Tativarru B.O</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>148</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>119</v>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>79.33333333333333</v>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Komatigunta Lock B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -1312,17 +1312,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,26 +1336,26 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>72</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
@@ -1411,17 +1411,17 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>273</v>
+        <v>112</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>68</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>68</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>68</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>64</v>
+        <v>63.33333333333333</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,26 +1600,26 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>63.33333333333333</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1633,26 +1633,26 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,26 +1666,26 @@
         <v>150</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
         <v>150</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>57.33333333333334</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
@@ -1814,10 +1814,10 @@
         <v>117</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -1831,23 +1831,23 @@
         <v>150</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>54</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>80</v>
@@ -1873,14 +1873,14 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>80</v>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -1996,23 +1996,23 @@
         <v>150</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>50</v>
+        <v>50.66666666666667</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>75</v>
@@ -2036,52 +2036,52 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>Pedakamanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H45" s="19" t="n">
-        <v>48.66666666666667</v>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Ponukumadu B.O</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -2095,26 +2095,26 @@
         <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>49.33333333333334</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -2128,26 +2128,26 @@
         <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -2161,26 +2161,26 @@
         <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>46</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -2227,26 +2227,26 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -2260,23 +2260,23 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D52" s="18" t="n">
         <v>66</v>
@@ -2335,17 +2335,17 @@
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -2359,26 +2359,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>42.66666666666667</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -2392,26 +2392,26 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>42</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -2425,26 +2425,26 @@
         <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,26 +2458,26 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>38</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>38</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,26 +2524,26 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>37.33333333333334</v>
+        <v>36</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -2557,26 +2557,26 @@
         <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>36</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>69</v>
+        <v>176</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,26 +2590,26 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>36</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         <v>150</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>34.66666666666667</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63">
@@ -2665,17 +2665,17 @@
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>32.66666666666666</v>
+        <v>32</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,26 +2722,26 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>22.66666666666666</v>
+        <v>32</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2755,26 +2755,26 @@
         <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>21.33333333333334</v>
+        <v>25.33333333333334</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>21.33333333333334</v>
+        <v>22.66666666666666</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C68" s="17" t="n">
         <v>50</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2821,26 +2821,26 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>20.66666666666667</v>
+        <v>22</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
         <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70">
@@ -2969,10 +2969,10 @@
         <v>6</v>
       </c>
       <c r="C73" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         <v>150</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-3.333333333333333</v>
+        <v>-4.666666666666667</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>1430</v>
+        <v>1457</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>918</v>
+        <v>947</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>1000</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="75">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>300</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>125.6666666666667</v>
+        <v>125.3333333333333</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>56</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>300</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>117.3333333333333</v>
+        <v>117.6666666666667</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3098,13 +3098,13 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>68</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>300</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>105.3333333333333</v>
+        <v>106</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0</v>
@@ -3127,17 +3127,17 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Moturu S.O</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="C78" s="8" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -3151,26 +3151,26 @@
         <v>300</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>99.33333333333333</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Rudrapaka S.O</t>
+          <t>Moturu S.O</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         <v>300</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>97.66666666666667</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>96</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         <v>300</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>90.33333333333333</v>
+        <v>92.33333333333333</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>538</v>
+        <v>561</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         <v>300</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>83.66666666666667</v>
+        <v>88</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82">
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C82" s="13" t="n">
         <v>31</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
@@ -3283,10 +3283,10 @@
         <v>300</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>71.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="B85" s="13" t="n">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C85" s="13" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         <v>300</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C86" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         <v>300</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>46</v>
+        <v>47.66666666666667</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="87">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C87" s="17" t="n">
         <v>62</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>300</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>39</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88">
@@ -3637,10 +3637,10 @@
         <v>239</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>130</v>
+        <v>123.3333333333333</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3670,10 +3670,10 @@
         <v>253</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>128.6666666666667</v>
+        <v>115.3333333333333</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -3927,17 +3927,17 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,26 +3951,26 @@
         <v>150</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>91.33333333333333</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>153</v>
+        <v>238</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3984,59 +3984,59 @@
         <v>150</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="C14" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>90.66666666666666</v>
+      </c>
+      <c r="I14" s="11" t="n">
         <v>14</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>132</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4050,26 +4050,26 @@
         <v>150</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>85.33333333333334</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -4083,26 +4083,26 @@
         <v>150</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -4116,26 +4116,26 @@
         <v>150</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>82.66666666666667</v>
+        <v>84</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -4149,26 +4149,26 @@
         <v>150</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>82</v>
+        <v>82.66666666666667</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -4182,43 +4182,43 @@
         <v>150</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>81.33333333333333</v>
+        <v>80.66666666666666</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Tativarru B.O</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>148</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>119</v>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>79.33333333333333</v>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Komatigunta Lock B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4290,17 +4290,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,26 +4314,26 @@
         <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>72</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
@@ -4389,17 +4389,17 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>273</v>
+        <v>112</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>68</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,26 +4446,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>68</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,26 +4479,26 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>65.33333333333333</v>
+        <v>68</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>64</v>
+        <v>63.33333333333333</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,26 +4578,26 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>63.33333333333333</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4611,26 +4611,26 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,26 +4644,26 @@
         <v>150</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -4677,10 +4677,10 @@
         <v>150</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>57.33333333333334</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
@@ -4792,10 +4792,10 @@
         <v>117</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -4809,23 +4809,23 @@
         <v>150</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>54</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>80</v>
@@ -4851,14 +4851,14 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>80</v>
@@ -4917,14 +4917,14 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>76</v>
@@ -4950,17 +4950,17 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -4974,10 +4974,10 @@
         <v>150</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>50</v>
+        <v>50.66666666666667</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44">
@@ -5014,52 +5014,52 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>Pedakamanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H45" s="19" t="n">
-        <v>48.66666666666667</v>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Chinayerukapadu B.O</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -5073,26 +5073,26 @@
         <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>49.33333333333334</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -5106,26 +5106,26 @@
         <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -5139,26 +5139,26 @@
         <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -5172,26 +5172,26 @@
         <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>46</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -5205,26 +5205,26 @@
         <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -5238,23 +5238,23 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D52" s="18" t="n">
         <v>66</v>
@@ -5313,17 +5313,17 @@
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -5337,26 +5337,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>42.66666666666667</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -5370,26 +5370,26 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>42</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -5403,26 +5403,26 @@
         <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,26 +5436,26 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>38</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,26 +5469,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>38</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>37.33333333333334</v>
+        <v>36</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -5535,26 +5535,26 @@
         <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>36</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,26 +5568,26 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>36</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -5601,10 +5601,10 @@
         <v>150</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>34.66666666666667</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63">
@@ -5643,17 +5643,17 @@
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>32.66666666666666</v>
+        <v>32</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,26 +5700,26 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>22.66666666666666</v>
+        <v>32</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5733,26 +5733,26 @@
         <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>21.33333333333334</v>
+        <v>25.33333333333334</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>170</v>
+        <v>53</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>21.33333333333334</v>
+        <v>22.66666666666666</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68">
@@ -5779,13 +5779,13 @@
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C68" s="17" t="n">
         <v>50</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5799,26 +5799,26 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>20.66666666666667</v>
+        <v>22</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
         <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70">
@@ -5947,10 +5947,10 @@
         <v>6</v>
       </c>
       <c r="C73" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -5964,10 +5964,10 @@
         <v>150</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-3.333333333333333</v>
+        <v>-4.666666666666667</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>125.6666666666667</v>
+        <v>125.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6084,13 +6084,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>56</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117.3333333333333</v>
+        <v>117.6666666666667</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>68</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>300</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>105.3333333333333</v>
+        <v>106</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6146,17 +6146,17 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Moturu S.O</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6170,26 +6170,26 @@
         <v>300</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>99.33333333333333</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Rudrapaka S.O</t>
+          <t>Moturu S.O</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6203,10 +6203,10 @@
         <v>300</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>97.66666666666667</v>
+        <v>97.33333333333334</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>96</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         <v>300</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>90.33333333333333</v>
+        <v>92.33333333333333</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>538</v>
+        <v>561</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6269,10 +6269,10 @@
         <v>300</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>83.66666666666667</v>
+        <v>88</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>31</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -6302,10 +6302,10 @@
         <v>300</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>71.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         <v>300</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>300</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>46</v>
+        <v>47.66666666666667</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="17" t="n">
         <v>62</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         <v>300</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>39</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15">
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1430</v>
+        <v>1457</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>918</v>
+        <v>947</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>1000</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -6763,10 +6763,10 @@
         <v>239</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>130</v>
+        <v>123.3333333333333</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6796,10 +6796,10 @@
         <v>253</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>128.6666666666667</v>
+        <v>115.3333333333333</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6969,10 +6969,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
         <v>150</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>-3.333333333333333</v>
+        <v>-4.666666666666667</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
@@ -7094,17 +7094,17 @@
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         <v>150</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>125.6666666666667</v>
+        <v>125.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>56</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117.3333333333333</v>
+        <v>117.6666666666667</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7271,13 +7271,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>68</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>300</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>105.3333333333333</v>
+        <v>106</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C4" s="17" t="n">
         <v>62</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         <v>300</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>39</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>15966</v>
+        <v>16234</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5602</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>10364</v>
+        <v>10419</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>146.6666666666667</v>
+        <v>149.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -656,13 +656,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>54</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>123.3333333333333</v>
+        <v>124</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -718,14 +718,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>167</v>
@@ -751,17 +751,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>150</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>109.3333333333333</v>
+        <v>111.3333333333333</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>189</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>150</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>109.3333333333333</v>
+        <v>106</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -817,14 +817,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>156</v>
@@ -850,17 +850,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -874,76 +874,76 @@
         <v>150</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>101.3333333333333</v>
+        <v>104</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Koyyagurapadu B.O</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>194</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>148</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>98.66666666666667</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>2</v>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Bokinala B.O</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>103.3333333333333</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>213</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>97.33333333333334</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>4</v>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Dosapadu B.O</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>101.3333333333333</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>19</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
         <v>150</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1006,26 +1006,26 @@
         <v>150</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>90.66666666666666</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1039,26 +1039,26 @@
         <v>150</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>90.66666666666666</v>
+        <v>94</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1072,26 +1072,26 @@
         <v>150</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>89.33333333333333</v>
+        <v>94</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1105,26 +1105,26 @@
         <v>150</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>88</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         <v>150</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>20</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
         <v>150</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>82.66666666666667</v>
+        <v>84.66666666666667</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>162</v>
+        <v>303</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1204,158 +1204,158 @@
         <v>150</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>80.66666666666666</v>
+        <v>84.66666666666667</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>Kanukollu B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>194</v>
-      </c>
-      <c r="C20" s="8" t="n">
+      <c r="B21" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="C21" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D21" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>80.66666666666666</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Putlacheruvu B.O</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>80.66666666666666</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Tativarru B.O</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>153</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H20" s="10" t="n">
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H23" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I23" s="11" t="n">
         <v>30</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Gunnanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>141</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Nandigamalanka B.O</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n">
-        <v>126</v>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>115</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>76.66666666666667</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Tativarru B.O</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>148</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>33</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>115</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>76.66666666666667</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,26 +1369,26 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>72</v>
+        <v>78.66666666666666</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>68.66666666666667</v>
+        <v>76</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>68.66666666666667</v>
+        <v>74</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>273</v>
+        <v>119</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>68</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>40</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>68</v>
+        <v>71.33333333333334</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>63.33333333333333</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,26 +1600,26 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1633,26 +1633,26 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,26 +1666,26 @@
         <v>150</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -1699,26 +1699,26 @@
         <v>150</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>57.33333333333334</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -1732,26 +1732,26 @@
         <v>150</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>56.66666666666666</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -1765,26 +1765,26 @@
         <v>150</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -1798,26 +1798,26 @@
         <v>150</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
         <v>150</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>54</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -1864,26 +1864,26 @@
         <v>150</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1897,26 +1897,26 @@
         <v>150</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>54</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1930,26 +1930,26 @@
         <v>150</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>54</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -1963,26 +1963,26 @@
         <v>150</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>50.66666666666667</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
         <v>150</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>50.66666666666667</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -2029,224 +2029,224 @@
         <v>150</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>50</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
+          <t>Koduru B.O</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>52.66666666666666</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Lakshminarasimhapuram B.O</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>51.33333333333333</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>50.66666666666667</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Chinayerukapadu B.O</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
           <t>Ponukumadu B.O</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B50" s="13" t="n">
         <v>102</v>
       </c>
-      <c r="C45" s="13" t="n">
+      <c r="C50" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="D45" s="14" t="n">
+      <c r="D50" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H45" s="15" t="n">
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H50" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I45" s="11" t="n">
+      <c r="I50" s="11" t="n">
         <v>75</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>Siddantham B.O</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="n">
-        <v>168</v>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>94</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G46" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>49.33333333333334</v>
-      </c>
-      <c r="I46" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>Addada B.O</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="n">
-        <v>115</v>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G47" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H47" s="19" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>Pedakamanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G48" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>Guraza B.O</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="n">
-        <v>96</v>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>71</v>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G49" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H49" s="19" t="n">
-        <v>47.33333333333334</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Dondapadu B.O</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="n">
-        <v>119</v>
-      </c>
-      <c r="C50" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>69</v>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G50" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H50" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="I50" s="11" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -2260,26 +2260,26 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>46</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -2293,26 +2293,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>44</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -2326,26 +2326,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>46</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -2359,26 +2359,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -2392,26 +2392,26 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -2425,26 +2425,26 @@
         <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>44</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,26 +2458,26 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>38</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>36.66666666666666</v>
+        <v>40</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,26 +2524,26 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>36</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -2557,26 +2557,26 @@
         <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,26 +2590,26 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -2623,26 +2623,26 @@
         <v>150</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>34.66666666666667</v>
+        <v>38</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -2656,26 +2656,26 @@
         <v>150</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>34.66666666666667</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>32</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>32</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66">
@@ -2764,17 +2764,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>22.66666666666666</v>
+        <v>24</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C68" s="17" t="n">
         <v>50</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2821,26 +2821,26 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>22</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -2854,26 +2854,26 @@
         <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>21.33333333333334</v>
+        <v>22.66666666666666</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         <v>150</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>14</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>1457</v>
+        <v>1508</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>947</v>
+        <v>972</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>1000</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>51</v>
+        <v>53.6</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75">
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D75" s="4" t="n">
         <v>376</v>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>56</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>300</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>117.6666666666667</v>
+        <v>123.6666666666667</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>35</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         <v>300</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>97.66666666666667</v>
+        <v>98.66666666666667</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         <v>300</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>97.33333333333334</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>96</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         <v>300</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>92.33333333333333</v>
+        <v>94</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3250,26 +3250,26 @@
         <v>300</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>88</v>
+        <v>88.33333333333333</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>Pedamaddali S.O</t>
+          <t>Indupalli S.O</t>
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>247</v>
+        <v>366</v>
       </c>
       <c r="C82" s="13" t="n">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
@@ -3283,26 +3283,26 @@
         <v>300</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>Indupalli S.O</t>
+          <t>Pedamaddali S.O</t>
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>340</v>
+        <v>247</v>
       </c>
       <c r="C83" s="13" t="n">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         <v>300</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>69.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="B85" s="13" t="n">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="C85" s="13" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         <v>300</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C86" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         <v>300</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>47.66666666666667</v>
+        <v>48</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C87" s="17" t="n">
         <v>62</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3448,26 +3448,26 @@
         <v>300</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>39</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Elamarru S.O</t>
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="C88" s="17" t="n">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3481,26 +3481,26 @@
         <v>300</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>Elamarru S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>300</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>33</v>
+        <v>34.33333333333334</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>146.6666666666667</v>
+        <v>149.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>54</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>123.3333333333333</v>
+        <v>124</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3696,14 +3696,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>167</v>
@@ -3729,17 +3729,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>150</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>109.3333333333333</v>
+        <v>111.3333333333333</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -3762,17 +3762,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>150</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>109.3333333333333</v>
+        <v>106</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -3795,14 +3795,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>156</v>
@@ -3828,17 +3828,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -3852,76 +3852,76 @@
         <v>150</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>101.3333333333333</v>
+        <v>104</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Koyyagurapadu B.O</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>194</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>148</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>98.66666666666667</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>2</v>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Bokinala B.O</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>103.3333333333333</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>213</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>97.33333333333334</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>4</v>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Dosapadu B.O</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>101.3333333333333</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>19</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,26 +3951,26 @@
         <v>150</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3984,26 +3984,26 @@
         <v>150</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>90.66666666666666</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -4017,26 +4017,26 @@
         <v>150</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>90.66666666666666</v>
+        <v>94</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4050,26 +4050,26 @@
         <v>150</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>89.33333333333333</v>
+        <v>94</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -4083,26 +4083,26 @@
         <v>150</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>88</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -4116,10 +4116,10 @@
         <v>150</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -4129,13 +4129,13 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>20</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -4149,26 +4149,26 @@
         <v>150</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>82.66666666666667</v>
+        <v>84.66666666666667</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>162</v>
+        <v>303</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -4182,158 +4182,158 @@
         <v>150</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>80.66666666666666</v>
+        <v>84.66666666666667</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>Kanukollu B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>Komatigunta Lock B.O</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>194</v>
-      </c>
-      <c r="C20" s="8" t="n">
+      <c r="B21" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="C21" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D21" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>80.66666666666666</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Putlacheruvu B.O</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>80.66666666666666</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Tativarru B.O</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>153</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H20" s="10" t="n">
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H23" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I23" s="11" t="n">
         <v>30</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Gunnanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>141</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Nandigamalanka B.O</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n">
-        <v>126</v>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>115</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>76.66666666666667</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Tativarru B.O</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>148</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>33</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>115</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>76.66666666666667</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,26 +4347,26 @@
         <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>72</v>
+        <v>78.66666666666666</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,26 +4380,26 @@
         <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>68.66666666666667</v>
+        <v>76</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,26 +4446,26 @@
         <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>68.66666666666667</v>
+        <v>74</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>273</v>
+        <v>119</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,26 +4479,26 @@
         <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>68</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>40</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>68</v>
+        <v>71.33333333333334</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>63.33333333333333</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,26 +4578,26 @@
         <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4611,26 +4611,26 @@
         <v>150</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,26 +4644,26 @@
         <v>150</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -4677,26 +4677,26 @@
         <v>150</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>57.33333333333334</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -4710,26 +4710,26 @@
         <v>150</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>56.66666666666666</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
         <v>112</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -4743,26 +4743,26 @@
         <v>150</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -4776,26 +4776,26 @@
         <v>150</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -4809,26 +4809,26 @@
         <v>150</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>54</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -4842,26 +4842,26 @@
         <v>150</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -4875,26 +4875,26 @@
         <v>150</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>54</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -4908,26 +4908,26 @@
         <v>150</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>54</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -4941,26 +4941,26 @@
         <v>150</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>50.66666666666667</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -4974,26 +4974,26 @@
         <v>150</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>50.66666666666667</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -5007,224 +5007,224 @@
         <v>150</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>50</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
+          <t>Dondapadu B.O</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>52.66666666666666</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Lakshminarasimhapuram B.O</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>51.33333333333333</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>50.66666666666667</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
           <t>Chinayerukapadu B.O</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B49" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="C45" s="13" t="n">
+      <c r="C49" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="D45" s="14" t="n">
+      <c r="D49" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H45" s="15" t="n">
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H49" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I45" s="11" t="n">
+      <c r="I49" s="11" t="n">
         <v>75</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>Siddantham B.O</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="n">
-        <v>168</v>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>94</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G46" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>49.33333333333334</v>
-      </c>
-      <c r="I46" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>Addada B.O</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="n">
-        <v>115</v>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G47" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H47" s="19" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>Pedakamanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G48" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>Guraza B.O</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="n">
-        <v>96</v>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>71</v>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G49" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H49" s="19" t="n">
-        <v>47.33333333333334</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>79</v>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Dondapadu B.O</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="n">
-        <v>119</v>
-      </c>
-      <c r="C50" s="17" t="n">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Ponukumadu B.O</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H50" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="D50" s="18" t="n">
-        <v>69</v>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G50" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H50" s="19" t="n">
-        <v>46</v>
-      </c>
       <c r="I50" s="11" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -5238,26 +5238,26 @@
         <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>46</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -5271,26 +5271,26 @@
         <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>44</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -5304,26 +5304,26 @@
         <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>46</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -5337,26 +5337,26 @@
         <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -5370,26 +5370,26 @@
         <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>45.33333333333333</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -5403,26 +5403,26 @@
         <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>44</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,26 +5436,26 @@
         <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>38</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,26 +5469,26 @@
         <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>36.66666666666666</v>
+        <v>40</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>36</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -5535,26 +5535,26 @@
         <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,26 +5568,26 @@
         <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -5601,26 +5601,26 @@
         <v>150</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>34.66666666666667</v>
+        <v>38</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -5634,26 +5634,26 @@
         <v>150</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>34.66666666666667</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>32</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,10 +5700,10 @@
         <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>32</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66">
@@ -5742,17 +5742,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
         <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>22.66666666666666</v>
+        <v>24</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68">
@@ -5779,13 +5779,13 @@
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C68" s="17" t="n">
         <v>50</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5799,26 +5799,26 @@
         <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>22</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5832,26 +5832,26 @@
         <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>21.33333333333334</v>
+        <v>22.66666666666666</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
         <v>150</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>14</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71">
@@ -6051,10 +6051,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>376</v>
@@ -6084,13 +6084,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>56</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117.6666666666667</v>
+        <v>123.6666666666667</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6150,13 +6150,13 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>35</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>300</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>97.66666666666667</v>
+        <v>98.66666666666667</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6183,13 +6183,13 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6203,10 +6203,10 @@
         <v>300</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>97.33333333333334</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>96</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         <v>300</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>92.33333333333333</v>
+        <v>94</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6269,26 +6269,26 @@
         <v>300</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>88</v>
+        <v>88.33333333333333</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Pedamaddali S.O</t>
+          <t>Indupalli S.O</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>247</v>
+        <v>366</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -6302,26 +6302,26 @@
         <v>300</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Indupalli S.O</t>
+          <t>Pedamaddali S.O</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>340</v>
+        <v>247</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         <v>300</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>69.66666666666667</v>
+        <v>72</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         <v>300</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>300</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>47.66666666666667</v>
+        <v>48</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="17" t="n">
         <v>62</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6467,26 +6467,26 @@
         <v>300</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>39</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Elamarru S.O</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6500,26 +6500,26 @@
         <v>300</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Elamarru S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>300</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>33</v>
+        <v>34.33333333333334</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1457</v>
+        <v>1508</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>947</v>
+        <v>972</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>1000</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>51</v>
+        <v>53.6</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>146.6666666666667</v>
+        <v>149.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6760,13 +6760,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>54</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>123.3333333333333</v>
+        <v>124</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>167</v>
@@ -6855,17 +6855,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>150</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>109.3333333333333</v>
+        <v>111.3333333333333</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -7061,17 +7061,17 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
@@ -7085,26 +7085,26 @@
         <v>150</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>14</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         <v>150</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>21.33333333333334</v>
+        <v>22.66666666666666</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>376</v>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>56</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117.6666666666667</v>
+        <v>123.6666666666667</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7374,17 +7374,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Elamarru S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,26 +7398,26 @@
         <v>300</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>33</v>
+        <v>34.33333333333334</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Elamarru S.O</t>
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         <v>300</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" s="17" t="n">
         <v>62</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         <v>300</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>39</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>16234</v>
+        <v>16728</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5815</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>10419</v>
+        <v>10812</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>116</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         <v>300</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>149.3333333333333</v>
+        <v>129.1428571428571</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -659,10 +659,10 @@
         <v>240</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>300</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>124</v>
+        <v>103.4285714285714</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -685,17 +685,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>253</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -706,260 +706,260 @@
         <v>300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>115.3333333333333</v>
+        <v>103.4285714285714</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Bhushanagulla B.O</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="C5" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>111.3333333333333</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
+      <c r="D5" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>98.28571428571429</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Vinnakota B.O</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>111.3333333333333</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0</v>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Appikatla B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>253</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>171</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>97.71428571428571</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Moparru B.O</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>184</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>94.28571428571428</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Bokinala B.O</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Bollapadu B.O</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B9" s="8" t="n">
         <v>189</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C9" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D9" s="9" t="n">
         <v>159</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Koyyagurapadu B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Moparru B.O</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>90.85714285714286</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Dosapadu B.O</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>196</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>89.71428571428571</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>176</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>103.3333333333333</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Dosapadu B.O</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>101.3333333333333</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0</v>
+      <c r="D11" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>89.71428571428571</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -970,29 +970,29 @@
         <v>300</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>96</v>
+        <v>86.28571428571429</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1003,29 +1003,29 @@
         <v>300</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>94.66666666666667</v>
+        <v>85.14285714285714</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>243</v>
+        <v>161</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1036,29 +1036,29 @@
         <v>300</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1069,13 +1069,13 @@
         <v>300</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>300</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>89.33333333333333</v>
+        <v>80.57142857142857</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1135,211 +1135,211 @@
         <v>300</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Lingavaram B.O</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="13" t="n">
         <v>147</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="14" t="n">
         <v>127</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>84.66666666666667</v>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>72.57142857142857</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Tenneru B.O</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="13" t="n">
         <v>303</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="13" t="n">
         <v>176</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="14" t="n">
         <v>127</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>84.66666666666667</v>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>72.57142857142857</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Kanukollu B.O</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="13" t="n">
         <v>183</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="13" t="n">
         <v>57</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="14" t="n">
         <v>126</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>84</v>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>72</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Komatigunta Lock B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>195</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>80.66666666666666</v>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Nandigamalanka B.O</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>72</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Putlacheruvu B.O</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>162</v>
-      </c>
-      <c r="C22" s="8" t="n">
+      <c r="B22" s="13" t="n">
+        <v>165</v>
+      </c>
+      <c r="C22" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>80.66666666666666</v>
+      <c r="D22" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>70.85714285714285</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Tativarru B.O</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="13" t="n">
         <v>153</v>
       </c>
-      <c r="C23" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>80</v>
+      <c r="C23" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>68</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
@@ -1366,29 +1366,29 @@
         <v>300</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>78.66666666666666</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1399,29 +1399,29 @@
         <v>300</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>76.66666666666667</v>
+        <v>66.28571428571428</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1432,29 +1432,29 @@
         <v>300</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>76</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1465,29 +1465,29 @@
         <v>300</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>74</v>
+        <v>65.14285714285715</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1498,26 +1498,26 @@
         <v>300</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>73.33333333333333</v>
+        <v>65.14285714285715</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>107</v>
@@ -1531,29 +1531,29 @@
         <v>300</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1564,29 +1564,29 @@
         <v>300</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>68.66666666666667</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1597,29 +1597,29 @@
         <v>300</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>67.33333333333333</v>
+        <v>60</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1630,29 +1630,29 @@
         <v>300</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>58.85714285714285</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1663,29 +1663,29 @@
         <v>300</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -1696,29 +1696,29 @@
         <v>300</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>55.42857142857143</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -1729,29 +1729,29 @@
         <v>300</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>54.85714285714286</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -1762,29 +1762,29 @@
         <v>300</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -1795,29 +1795,29 @@
         <v>300</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>56.66666666666666</v>
+        <v>53.71428571428572</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -1828,29 +1828,29 @@
         <v>300</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>53.71428571428572</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -1861,29 +1861,29 @@
         <v>300</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>53.14285714285715</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1894,29 +1894,29 @@
         <v>300</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>54</v>
+        <v>53.14285714285715</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1927,29 +1927,29 @@
         <v>300</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>54</v>
+        <v>52.57142857142857</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -1960,29 +1960,29 @@
         <v>300</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>51.42857142857142</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         <v>300</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>51.42857142857142</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>50</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -2026,29 +2026,29 @@
         <v>300</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>50.85714285714285</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
@@ -2059,29 +2059,29 @@
         <v>300</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>50.85714285714285</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
@@ -2092,161 +2092,161 @@
         <v>300</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>52</v>
+        <v>50.28571428571429</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="n">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Komarru B.O</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>49.71428571428572</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>49.71428571428572</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Chinayerukapadu B.O</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D49" s="18" t="n">
         <v>86</v>
       </c>
-      <c r="C47" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>77</v>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>51.33333333333333</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n">
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>49.14285714285715</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Edulamaddali B.O</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>185</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="D50" s="18" t="n">
         <v>84</v>
       </c>
-      <c r="C48" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>76</v>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G48" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>50.66666666666667</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Chinayerukapadu B.O</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="n">
-        <v>110</v>
-      </c>
-      <c r="C49" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>75</v>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G49" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Ponukumadu B.O</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="n">
-        <v>102</v>
-      </c>
-      <c r="C50" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>75</v>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F50" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G50" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>50</v>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>48</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -2257,29 +2257,29 @@
         <v>300</v>
       </c>
       <c r="G51" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>48.66666666666667</v>
+        <v>48</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -2290,62 +2290,62 @@
         <v>300</v>
       </c>
       <c r="G52" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>47.42857142857143</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>81</v>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>46.28571428571428</v>
+      </c>
+      <c r="I53" s="11" t="n">
         <v>94</v>
-      </c>
-      <c r="C53" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>69</v>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G53" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -2356,29 +2356,29 @@
         <v>300</v>
       </c>
       <c r="G54" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>45.33333333333333</v>
+        <v>45.14285714285714</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -2389,29 +2389,29 @@
         <v>300</v>
       </c>
       <c r="G55" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>45.33333333333333</v>
+        <v>45.14285714285714</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -2422,29 +2422,29 @@
         <v>300</v>
       </c>
       <c r="G56" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>44</v>
+        <v>44.57142857142857</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2455,29 +2455,29 @@
         <v>300</v>
       </c>
       <c r="G57" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>42.28571428571428</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2488,29 +2488,29 @@
         <v>300</v>
       </c>
       <c r="G58" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>40</v>
+        <v>41.71428571428572</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2521,29 +2521,29 @@
         <v>300</v>
       </c>
       <c r="G59" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -2554,29 +2554,29 @@
         <v>300</v>
       </c>
       <c r="G60" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>37.14285714285715</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2587,29 +2587,29 @@
         <v>300</v>
       </c>
       <c r="G61" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>35.42857142857142</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -2620,29 +2620,29 @@
         <v>300</v>
       </c>
       <c r="G62" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>38</v>
+        <v>34.28571428571428</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -2653,29 +2653,29 @@
         <v>300</v>
       </c>
       <c r="G63" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>36.66666666666666</v>
+        <v>33.14285714285714</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2686,29 +2686,29 @@
         <v>300</v>
       </c>
       <c r="G64" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2719,29 +2719,29 @@
         <v>300</v>
       </c>
       <c r="G65" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>30.66666666666666</v>
+        <v>30.28571428571429</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2752,29 +2752,29 @@
         <v>300</v>
       </c>
       <c r="G66" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>25.33333333333334</v>
+        <v>30.28571428571429</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2785,13 +2785,13 @@
         <v>300</v>
       </c>
       <c r="G67" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>24</v>
+        <v>29.14285714285714</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C68" s="17" t="n">
         <v>50</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>300</v>
       </c>
       <c r="G68" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>23.33333333333333</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69">
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -2851,29 +2851,29 @@
         <v>300</v>
       </c>
       <c r="G69" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>22.66666666666666</v>
+        <v>21.71428571428572</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>300</v>
       </c>
       <c r="G70" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>21.14285714285714</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71">
@@ -2900,13 +2900,13 @@
         </is>
       </c>
       <c r="B71" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C71" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         <v>300</v>
       </c>
       <c r="G71" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>6</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72">
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C72" s="17" t="n">
         <v>267</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -2950,13 +2950,13 @@
         <v>300</v>
       </c>
       <c r="G72" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>3.333333333333333</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -2983,62 +2983,62 @@
         <v>300</v>
       </c>
       <c r="G73" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-4.666666666666667</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>157</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B74" s="13" t="n">
-        <v>1508</v>
-      </c>
-      <c r="C74" s="13" t="n">
-        <v>972</v>
-      </c>
-      <c r="D74" s="14" t="n">
-        <v>536</v>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="B74" s="17" t="n">
+        <v>1541</v>
+      </c>
+      <c r="C74" s="17" t="n">
+        <v>990</v>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>551</v>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F74" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="G74" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H74" s="15" t="n">
-        <v>53.6</v>
+      <c r="G74" s="17" t="n">
+        <v>1166.666666666667</v>
+      </c>
+      <c r="H74" s="19" t="n">
+        <v>47.22857142857143</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>464</v>
+        <v>615.6666666666667</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Angaluru S.O</t>
+          <t>Ventrapragada S.O</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3049,10 +3049,10 @@
         <v>600</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>125.3333333333333</v>
+        <v>115.7142857142857</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3061,17 +3061,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Ventrapragada S.O</t>
+          <t>Angaluru S.O</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>427</v>
+        <v>488</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3082,46 +3082,46 @@
         <v>600</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>123.6666666666667</v>
+        <v>112.2857142857143</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>Vunguturu S.O (Krishna)</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
-        <v>386</v>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>318</v>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="B77" s="8" t="n">
+        <v>389</v>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>320</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G77" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="I77" s="6" t="n">
-        <v>0</v>
+      <c r="G77" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="H77" s="10" t="n">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="I77" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="78">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>35</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -3148,13 +3148,13 @@
         <v>600</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>98.66666666666667</v>
+        <v>87.42857142857143</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -3181,13 +3181,13 @@
         <v>600</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>97.66666666666667</v>
+        <v>85.42857142857143</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3214,46 +3214,46 @@
         <v>600</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>94</v>
+        <v>85.42857142857143</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
+      <c r="A81" s="12" t="inlineStr">
         <is>
           <t>Mudinepalli S.O</t>
         </is>
       </c>
-      <c r="B81" s="8" t="n">
-        <v>572</v>
-      </c>
-      <c r="C81" s="8" t="n">
-        <v>307</v>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>265</v>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="B81" s="13" t="n">
+        <v>582</v>
+      </c>
+      <c r="C81" s="13" t="n">
+        <v>321</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>261</v>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n">
+      <c r="F81" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G81" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="H81" s="10" t="n">
-        <v>88.33333333333333</v>
+      <c r="G81" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>74.57142857142857</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82">
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C82" s="13" t="n">
         <v>132</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
@@ -3280,13 +3280,13 @@
         <v>600</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>78</v>
+        <v>68.28571428571428</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>66</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C83" s="13" t="n">
         <v>31</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3313,29 +3313,29 @@
         <v>600</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>72</v>
+        <v>62.57142857142857</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>Manikonda S.O</t>
+          <t>Rajendranagar Colony S.O</t>
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>233</v>
+        <v>427</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>56</v>
+        <v>247</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
@@ -3346,46 +3346,46 @@
         <v>600</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H84" s="15" t="n">
+        <v>51.42857142857142</v>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>Manikonda S.O</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="n">
+        <v>233</v>
+      </c>
+      <c r="C85" s="17" t="n">
         <v>59</v>
       </c>
-      <c r="I84" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>Rajendranagar Colony S.O</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n">
-        <v>416</v>
-      </c>
-      <c r="C85" s="13" t="n">
-        <v>242</v>
-      </c>
-      <c r="D85" s="14" t="n">
+      <c r="D85" s="18" t="n">
         <v>174</v>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E85" s="16" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F85" s="13" t="n">
+      <c r="F85" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="G85" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="H85" s="15" t="n">
-        <v>57.99999999999999</v>
+      <c r="G85" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="H85" s="19" t="n">
+        <v>49.71428571428572</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>126</v>
+        <v>176</v>
       </c>
     </row>
     <row r="86">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C86" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3412,13 +3412,13 @@
         <v>600</v>
       </c>
       <c r="G86" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>48</v>
+        <v>41.42857142857143</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>156</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C87" s="17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3445,29 +3445,29 @@
         <v>600</v>
       </c>
       <c r="G87" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>40.28571428571428</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>182</v>
+        <v>209</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>Elamarru S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="C88" s="17" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3478,29 +3478,29 @@
         <v>600</v>
       </c>
       <c r="G88" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>195</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Elamarru S.O</t>
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3511,13 +3511,13 @@
         <v>600</v>
       </c>
       <c r="G89" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>34.33333333333334</v>
+        <v>30.28571428571429</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>197</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>116</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         <v>300</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>149.3333333333333</v>
+        <v>129.1428571428571</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3637,10 +3637,10 @@
         <v>240</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3651,10 +3651,10 @@
         <v>300</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>124</v>
+        <v>103.4285714285714</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3663,17 +3663,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>253</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3684,260 +3684,260 @@
         <v>300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>115.3333333333333</v>
+        <v>103.4285714285714</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Bhushanagulla B.O</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="C5" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>111.3333333333333</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
+      <c r="D5" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>98.28571428571429</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Vinnakota B.O</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>111.3333333333333</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0</v>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Appikatla B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>253</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>171</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>97.71428571428571</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Moparru B.O</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>184</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>94.28571428571428</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Bokinala B.O</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Bollapadu B.O</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B9" s="8" t="n">
         <v>189</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C9" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D9" s="9" t="n">
         <v>159</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Koyyagurapadu B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Moparru B.O</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>90.85714285714286</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>176</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>103.3333333333333</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0</v>
+      <c r="D10" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>89.71428571428571</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Dosapadu B.O</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>101.3333333333333</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0</v>
+      <c r="B11" s="8" t="n">
+        <v>196</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>89.71428571428571</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3948,29 +3948,29 @@
         <v>300</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>96</v>
+        <v>86.28571428571429</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3981,13 +3981,13 @@
         <v>300</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>94.66666666666667</v>
+        <v>85.14285714285714</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -4014,29 +4014,29 @@
         <v>300</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4047,13 +4047,13 @@
         <v>300</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -4063,13 +4063,13 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -4080,13 +4080,13 @@
         <v>300</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>89.33333333333333</v>
+        <v>80.57142857142857</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -4113,211 +4113,211 @@
         <v>300</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Lingavaram B.O</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="13" t="n">
         <v>147</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="14" t="n">
         <v>127</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>84.66666666666667</v>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>72.57142857142857</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Tenneru B.O</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="13" t="n">
         <v>303</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="13" t="n">
         <v>176</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="14" t="n">
         <v>127</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>84.66666666666667</v>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>72.57142857142857</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Nandigamalanka B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Kanukollu B.O</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B21" s="13" t="n">
         <v>183</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C21" s="13" t="n">
         <v>57</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D21" s="14" t="n">
         <v>126</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Komatigunta Lock B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>195</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>80.66666666666666</v>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>72</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Putlacheruvu B.O</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>162</v>
-      </c>
-      <c r="C22" s="8" t="n">
+      <c r="B22" s="13" t="n">
+        <v>165</v>
+      </c>
+      <c r="C22" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>80.66666666666666</v>
+      <c r="D22" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>70.85714285714285</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Tativarru B.O</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="13" t="n">
         <v>153</v>
       </c>
-      <c r="C23" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>80</v>
+      <c r="C23" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>68</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
@@ -4344,29 +4344,29 @@
         <v>300</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>78.66666666666666</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4377,29 +4377,29 @@
         <v>300</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>76.66666666666667</v>
+        <v>66.28571428571428</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4410,29 +4410,29 @@
         <v>300</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>76</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4443,29 +4443,29 @@
         <v>300</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>74</v>
+        <v>65.14285714285715</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4476,13 +4476,13 @@
         <v>300</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>73.33333333333333</v>
+        <v>65.14285714285715</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
@@ -4509,29 +4509,29 @@
         <v>300</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>71.33333333333334</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4542,29 +4542,29 @@
         <v>300</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>68.66666666666667</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4575,29 +4575,29 @@
         <v>300</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>67.33333333333333</v>
+        <v>60</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4608,29 +4608,29 @@
         <v>300</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>58.85714285714285</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4641,13 +4641,13 @@
         <v>300</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>58.66666666666666</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>54</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -4674,29 +4674,29 @@
         <v>300</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>55.42857142857143</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -4707,29 +4707,29 @@
         <v>300</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>54.85714285714286</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
         <v>112</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -4740,29 +4740,29 @@
         <v>300</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -4773,29 +4773,29 @@
         <v>300</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>56.66666666666666</v>
+        <v>53.71428571428572</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -4806,29 +4806,29 @@
         <v>300</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>53.71428571428572</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -4839,13 +4839,13 @@
         <v>300</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>55.33333333333334</v>
+        <v>53.14285714285715</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>63</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -4872,29 +4872,29 @@
         <v>300</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>54</v>
+        <v>53.14285714285715</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -4905,29 +4905,29 @@
         <v>300</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>54</v>
+        <v>52.57142857142857</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -4938,29 +4938,29 @@
         <v>300</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>51.42857142857142</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -4971,29 +4971,29 @@
         <v>300</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>53.33333333333334</v>
+        <v>51.42857142857142</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>300</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>50.85714285714285</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45">
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C45" s="13" t="n">
         <v>50</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
@@ -5037,29 +5037,29 @@
         <v>300</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>52.66666666666666</v>
+        <v>50.85714285714285</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
@@ -5070,161 +5070,161 @@
         <v>300</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>52</v>
+        <v>50.28571428571429</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>49.71428571428572</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Komarru B.O</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>49.71428571428572</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Chinayerukapadu B.O</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>49.14285714285715</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
-      <c r="B47" s="13" t="n">
-        <v>86</v>
-      </c>
-      <c r="C47" s="13" t="n">
+      <c r="B50" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="C50" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="D47" s="14" t="n">
-        <v>77</v>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>51.33333333333333</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n">
+      <c r="D50" s="18" t="n">
         <v>84</v>
       </c>
-      <c r="C48" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>76</v>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G48" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>50.66666666666667</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Chinayerukapadu B.O</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="n">
-        <v>110</v>
-      </c>
-      <c r="C49" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>75</v>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G49" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Ponukumadu B.O</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="n">
-        <v>102</v>
-      </c>
-      <c r="C50" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>75</v>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F50" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G50" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>50</v>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>48</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -5235,29 +5235,29 @@
         <v>300</v>
       </c>
       <c r="G51" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>48.66666666666667</v>
+        <v>48</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -5268,62 +5268,62 @@
         <v>300</v>
       </c>
       <c r="G52" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>47.33333333333334</v>
+        <v>47.42857142857143</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>81</v>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>46.28571428571428</v>
+      </c>
+      <c r="I53" s="11" t="n">
         <v>94</v>
-      </c>
-      <c r="C53" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>69</v>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G53" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -5334,29 +5334,29 @@
         <v>300</v>
       </c>
       <c r="G54" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>45.33333333333333</v>
+        <v>45.14285714285714</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -5367,29 +5367,29 @@
         <v>300</v>
       </c>
       <c r="G55" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>45.33333333333333</v>
+        <v>45.14285714285714</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -5400,29 +5400,29 @@
         <v>300</v>
       </c>
       <c r="G56" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>44</v>
+        <v>44.57142857142857</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5433,29 +5433,29 @@
         <v>300</v>
       </c>
       <c r="G57" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>43.33333333333334</v>
+        <v>42.28571428571428</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5466,29 +5466,29 @@
         <v>300</v>
       </c>
       <c r="G58" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>40</v>
+        <v>41.71428571428572</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5499,29 +5499,29 @@
         <v>300</v>
       </c>
       <c r="G59" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -5532,29 +5532,29 @@
         <v>300</v>
       </c>
       <c r="G60" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>37.14285714285715</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5565,29 +5565,29 @@
         <v>300</v>
       </c>
       <c r="G61" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>38.66666666666666</v>
+        <v>35.42857142857142</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -5598,29 +5598,29 @@
         <v>300</v>
       </c>
       <c r="G62" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>38</v>
+        <v>34.28571428571428</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -5631,29 +5631,29 @@
         <v>300</v>
       </c>
       <c r="G63" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>36.66666666666666</v>
+        <v>33.14285714285714</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5664,29 +5664,29 @@
         <v>300</v>
       </c>
       <c r="G64" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>35.33333333333334</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>64</v>
+        <v>155</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5697,29 +5697,29 @@
         <v>300</v>
       </c>
       <c r="G65" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>30.66666666666666</v>
+        <v>30.28571428571429</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5730,29 +5730,29 @@
         <v>300</v>
       </c>
       <c r="G66" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>25.33333333333334</v>
+        <v>30.28571428571429</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5763,13 +5763,13 @@
         <v>300</v>
       </c>
       <c r="G67" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>24</v>
+        <v>29.14285714285714</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68">
@@ -5779,13 +5779,13 @@
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C68" s="17" t="n">
         <v>50</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5796,13 +5796,13 @@
         <v>300</v>
       </c>
       <c r="G68" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>23.33333333333333</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5829,29 +5829,29 @@
         <v>300</v>
       </c>
       <c r="G69" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>22.66666666666666</v>
+        <v>21.71428571428572</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -5862,13 +5862,13 @@
         <v>300</v>
       </c>
       <c r="G70" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>21.14285714285714</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71">
@@ -5878,13 +5878,13 @@
         </is>
       </c>
       <c r="B71" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C71" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -5895,13 +5895,13 @@
         <v>300</v>
       </c>
       <c r="G71" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>6</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72">
@@ -5911,13 +5911,13 @@
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C72" s="17" t="n">
         <v>267</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -5928,13 +5928,13 @@
         <v>300</v>
       </c>
       <c r="G72" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>3.333333333333333</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73">
@@ -5944,13 +5944,13 @@
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -5961,13 +5961,13 @@
         <v>300</v>
       </c>
       <c r="G73" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-4.666666666666667</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>157</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -6047,17 +6047,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Angaluru S.O</t>
+          <t>Ventrapragada S.O</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         <v>600</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>125.3333333333333</v>
+        <v>115.7142857142857</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6080,17 +6080,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ventrapragada S.O</t>
+          <t>Angaluru S.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>427</v>
+        <v>488</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6101,46 +6101,46 @@
         <v>600</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>123.6666666666667</v>
+        <v>112.2857142857143</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Vunguturu S.O (Krishna)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>386</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>318</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="8" t="n">
+        <v>389</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>320</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
+      <c r="G4" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -6150,13 +6150,13 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>35</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6167,29 +6167,29 @@
         <v>600</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>98.66666666666667</v>
+        <v>87.42857142857143</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Moturu S.O</t>
+          <t>Mudunuru S.O</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6200,29 +6200,29 @@
         <v>600</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>97.66666666666667</v>
+        <v>85.42857142857143</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Mudunuru S.O</t>
+          <t>Moturu S.O</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6233,46 +6233,46 @@
         <v>600</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>94</v>
+        <v>85.42857142857143</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Mudinepalli S.O</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>572</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>307</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>265</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="B8" s="13" t="n">
+        <v>582</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>321</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>261</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>88.33333333333333</v>
+      <c r="G8" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>74.57142857142857</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>132</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -6299,13 +6299,13 @@
         <v>600</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>78</v>
+        <v>68.28571428571428</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>66</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>31</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6332,29 +6332,29 @@
         <v>600</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>72</v>
+        <v>62.57142857142857</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Manikonda S.O</t>
+          <t>Rajendranagar Colony S.O</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>233</v>
+        <v>427</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>56</v>
+        <v>247</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6365,46 +6365,46 @@
         <v>600</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H11" s="15" t="n">
+        <v>51.42857142857142</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Manikonda S.O</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>233</v>
+      </c>
+      <c r="C12" s="17" t="n">
         <v>59</v>
       </c>
-      <c r="I11" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Rajendranagar Colony S.O</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>416</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>242</v>
-      </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="18" t="n">
         <v>174</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="G12" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>57.99999999999999</v>
+      <c r="G12" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>49.71428571428572</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>126</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6431,13 +6431,13 @@
         <v>600</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>48</v>
+        <v>41.42857142857143</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>156</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6464,29 +6464,29 @@
         <v>600</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>40.28571428571428</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>182</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Elamarru S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6497,29 +6497,29 @@
         <v>600</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>195</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Elamarru S.O</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6530,13 +6530,13 @@
         <v>600</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>34.33333333333334</v>
+        <v>30.28571428571429</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>197</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -6614,36 +6614,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
-        <v>1508</v>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>972</v>
-      </c>
-      <c r="D2" s="14" t="n">
-        <v>536</v>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="B2" s="17" t="n">
+        <v>1541</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>990</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>551</v>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F2" s="13" t="n">
+      <c r="F2" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="G2" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H2" s="15" t="n">
-        <v>53.6</v>
+      <c r="G2" s="17" t="n">
+        <v>1166.666666666667</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>47.22857142857143</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>464</v>
+        <v>615.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>116</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6744,10 +6744,10 @@
         <v>300</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>149.3333333333333</v>
+        <v>129.1428571428571</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6763,10 +6763,10 @@
         <v>240</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
         <v>300</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>124</v>
+        <v>103.4285714285714</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6789,17 +6789,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>253</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6810,10 +6810,10 @@
         <v>300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>115.3333333333333</v>
+        <v>103.4285714285714</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6826,13 +6826,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>19</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6843,29 +6843,29 @@
         <v>300</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>111.3333333333333</v>
+        <v>98.28571428571429</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6876,13 +6876,13 @@
         <v>300</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>111.3333333333333</v>
+        <v>97.71428571428571</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6983,13 +6983,13 @@
         <v>300</v>
       </c>
       <c r="G2" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>-4.666666666666667</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>157</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3">
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C3" s="17" t="n">
         <v>267</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7016,13 +7016,13 @@
         <v>300</v>
       </c>
       <c r="G3" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>3.333333333333333</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
@@ -7032,13 +7032,13 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="17" t="n">
         <v>14</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7049,29 +7049,29 @@
         <v>300</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>6</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
@@ -7082,13 +7082,13 @@
         <v>300</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>18.66666666666667</v>
+        <v>21.14285714285714</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6">
@@ -7098,13 +7098,13 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -7115,13 +7115,13 @@
         <v>300</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>22.66666666666666</v>
+        <v>21.71428571428572</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -7201,17 +7201,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Angaluru S.O</t>
+          <t>Ventrapragada S.O</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7222,10 +7222,10 @@
         <v>600</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>125.3333333333333</v>
+        <v>115.7142857142857</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7234,17 +7234,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ventrapragada S.O</t>
+          <t>Angaluru S.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>427</v>
+        <v>488</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7255,10 +7255,10 @@
         <v>600</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>123.6666666666667</v>
+        <v>112.2857142857143</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7271,13 +7271,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7288,13 +7288,13 @@
         <v>600</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>106</v>
+        <v>91.42857142857143</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -7374,17 +7374,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Elamarru S.O</t>
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7395,29 +7395,29 @@
         <v>600</v>
       </c>
       <c r="G2" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>34.33333333333334</v>
+        <v>30.28571428571429</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>197</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Elamarru S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7428,13 +7428,13 @@
         <v>600</v>
       </c>
       <c r="G3" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>195</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7461,13 +7461,13 @@
         <v>600</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>39.33333333333333</v>
+        <v>40.28571428571428</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>182</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>16728</v>
+        <v>17491</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5916</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>10812</v>
+        <v>11435</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>342</v>
+        <v>442</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>226</v>
+        <v>325</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>129.1428571428571</v>
+        <v>185.7142857142857</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -652,17 +652,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>108.5714285714286</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -709,191 +709,191 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>108</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Bhushanagulla B.O</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="C5" s="8" t="n">
+      <c r="B5" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>172</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>98.28571428571429</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>3</v>
+      <c r="D5" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>106.2857142857143</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Appikatla B.O</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>253</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>171</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>97.71428571428571</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>4</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Tummalapalli B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>103.4285714285714</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Moparru B.O</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>184</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>165</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>94.28571428571428</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>10</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Bokinala B.O</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>100.5714285714286</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Koyyagurapadu B.O</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="C8" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>160</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>91.42857142857143</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>15</v>
+      <c r="C8" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>100.5714285714286</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Bollapadu B.O</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>189</v>
-      </c>
-      <c r="C9" s="8" t="n">
+      <c r="B9" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>159</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>90.85714285714286</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>16</v>
+      <c r="D9" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -907,26 +907,26 @@
         <v>175</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>89.71428571428571</v>
+        <v>94.28571428571428</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -940,26 +940,26 @@
         <v>175</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>89.71428571428571</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
         <v>175</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>86.28571428571429</v>
+        <v>91.42857142857143</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1006,26 +1006,26 @@
         <v>175</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>85.14285714285714</v>
+        <v>90.85714285714286</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         <v>175</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>84</v>
+        <v>90.28571428571428</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1072,26 +1072,26 @@
         <v>175</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>84</v>
+        <v>89.71428571428571</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1105,26 +1105,26 @@
         <v>175</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>80.57142857142857</v>
+        <v>86.28571428571429</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1138,92 +1138,92 @@
         <v>175</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>80</v>
+        <v>84.57142857142857</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Lingavaram B.O</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>147</v>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>72.57142857142857</v>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Nandigamalanka B.O</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>83.42857142857143</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Tenneru B.O</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>303</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>176</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>72.57142857142857</v>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Kanukollu B.O</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>82.28571428571428</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1237,26 +1237,26 @@
         <v>175</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>72</v>
+        <v>78.85714285714286</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1270,59 +1270,59 @@
         <v>175</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>72</v>
+        <v>77.71428571428571</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C22" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>76.57142857142857</v>
+      </c>
+      <c r="I22" s="11" t="n">
         <v>41</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>124</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>70.85714285714285</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,26 +1336,26 @@
         <v>175</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>68</v>
+        <v>73.71428571428571</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,26 +1369,26 @@
         <v>175</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>67.42857142857143</v>
+        <v>73.14285714285714</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
         <v>175</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>66.28571428571428</v>
+        <v>72.57142857142857</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>175</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>65.71428571428571</v>
+        <v>72</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         <v>175</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>65.14285714285715</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         <v>175</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>65.14285714285715</v>
+        <v>69.14285714285714</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>136</v>
+        <v>318</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>175</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>69.14285714285714</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>175</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,59 +1600,59 @@
         <v>175</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>60</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="C32" s="13" t="n">
+        <v>123</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="I32" s="11" t="n">
         <v>58</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>103</v>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>58.85714285714285</v>
-      </c>
-      <c r="I32" s="11" t="n">
-        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,26 +1666,26 @@
         <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>63.42857142857142</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -1699,26 +1699,26 @@
         <v>175</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>55.42857142857143</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>219</v>
+        <v>142</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -1732,26 +1732,26 @@
         <v>175</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>54.85714285714286</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -1765,26 +1765,26 @@
         <v>175</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>54.28571428571428</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -1798,26 +1798,26 @@
         <v>175</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
         <v>175</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -1864,26 +1864,26 @@
         <v>175</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>53.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1897,26 +1897,26 @@
         <v>175</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>53.14285714285715</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1930,26 +1930,26 @@
         <v>175</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>52.57142857142857</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>111</v>
+        <v>205</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -1963,26 +1963,26 @@
         <v>175</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>51.42857142857142</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
         <v>175</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>51.42857142857142</v>
+        <v>56.57142857142857</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -2029,26 +2029,26 @@
         <v>175</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>50.85714285714285</v>
+        <v>56.57142857142857</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
@@ -2062,356 +2062,356 @@
         <v>175</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>50.85714285714285</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
+          <t>Polukonda B.O</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>55.42857142857143</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Chinapalaparru B.O</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>53.71428571428572</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Lakshminarasimhapuram B.O</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>53.71428571428572</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>53.71428571428572</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Edulamaddali B.O</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>194</v>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>53.14285714285715</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Koduru B.O</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>52.57142857142857</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
           <t>Pedaparupudi B.O</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n">
-        <v>124</v>
-      </c>
-      <c r="C46" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="D46" s="14" t="n">
+      <c r="B52" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Ramapuram B.O</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>51.42857142857142</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Siddantham B.O</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="n">
+        <v>186</v>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>50.85714285714285</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="C55" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="14" t="n">
         <v>88</v>
       </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H46" s="15" t="n">
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H55" s="15" t="n">
         <v>50.28571428571429</v>
       </c>
-      <c r="I46" s="11" t="n">
+      <c r="I55" s="11" t="n">
         <v>87</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>Komarru B.O</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="n">
-        <v>130</v>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>87</v>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G47" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H47" s="19" t="n">
-        <v>49.71428571428572</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="n">
-        <v>95</v>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>87</v>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G48" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>49.71428571428572</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>Chinayerukapadu B.O</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="n">
-        <v>121</v>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G49" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H49" s="19" t="n">
-        <v>49.14285714285715</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Edulamaddali B.O</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="n">
-        <v>185</v>
-      </c>
-      <c r="C50" s="17" t="n">
-        <v>101</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G50" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H50" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I50" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="n">
-        <v>93</v>
-      </c>
-      <c r="C51" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G51" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H51" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>Chinapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="n">
-        <v>113</v>
-      </c>
-      <c r="C52" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D52" s="18" t="n">
-        <v>83</v>
-      </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G52" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H52" s="19" t="n">
-        <v>47.42857142857143</v>
-      </c>
-      <c r="I52" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>Serikalavapudi B.O</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="n">
-        <v>109</v>
-      </c>
-      <c r="C53" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>81</v>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G53" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>46.28571428571428</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>Dandiganapudi B.O</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="C54" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D54" s="18" t="n">
-        <v>79</v>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G54" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H54" s="19" t="n">
-        <v>45.14285714285714</v>
-      </c>
-      <c r="I54" s="11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>Koduru B.O</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="n">
-        <v>115</v>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>36</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>79</v>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G55" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H55" s="19" t="n">
-        <v>45.14285714285714</v>
-      </c>
-      <c r="I55" s="11" t="n">
-        <v>96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -2425,26 +2425,26 @@
         <v>175</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>44.57142857142857</v>
+        <v>49.71428571428572</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,26 +2458,26 @@
         <v>175</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>42.28571428571428</v>
+        <v>49.71428571428572</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
         <v>175</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>41.71428571428572</v>
+        <v>47.42857142857143</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,59 +2524,59 @@
         <v>175</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>40.57142857142857</v>
+        <v>47.42857142857143</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>45.71428571428572</v>
+      </c>
+      <c r="I60" s="11" t="n">
         <v>95</v>
-      </c>
-      <c r="C60" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>65</v>
-      </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G60" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H60" s="19" t="n">
-        <v>37.14285714285715</v>
-      </c>
-      <c r="I60" s="11" t="n">
-        <v>110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,26 +2590,26 @@
         <v>175</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>35.42857142857142</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -2623,26 +2623,26 @@
         <v>175</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>34.28571428571428</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -2656,26 +2656,26 @@
         <v>175</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>33.14285714285714</v>
+        <v>38.85714285714285</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>175</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>31.42857142857143</v>
+        <v>38.85714285714285</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,26 +2722,26 @@
         <v>175</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>30.28571428571429</v>
+        <v>37.71428571428572</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         <v>175</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>30.28571428571429</v>
+        <v>34.28571428571428</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67">
@@ -2768,13 +2768,13 @@
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,26 +2788,26 @@
         <v>175</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>29.14285714285714</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>93</v>
+        <v>315</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>50</v>
+        <v>269</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         <v>175</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>24.57142857142857</v>
+        <v>26.28571428571428</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69">
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C69" s="17" t="n">
         <v>20</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -2854,26 +2854,26 @@
         <v>175</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>21.71428571428572</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -2887,26 +2887,26 @@
         <v>175</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>21.14285714285714</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Anamanapudi B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B71" s="17" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C71" s="17" t="n">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -2920,26 +2920,26 @@
         <v>175</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>5.714285714285714</v>
+        <v>23.42857142857143</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Anamanapudi B.O</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         <v>175</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>4.571428571428571</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C73" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -2986,59 +2986,59 @@
         <v>175</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-3.428571428571429</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B74" s="17" t="n">
-        <v>1541</v>
-      </c>
-      <c r="C74" s="17" t="n">
-        <v>990</v>
-      </c>
-      <c r="D74" s="18" t="n">
-        <v>551</v>
-      </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="B74" s="13" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C74" s="13" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>584</v>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F74" s="17" t="n">
+      <c r="F74" s="13" t="n">
         <v>2000</v>
       </c>
-      <c r="G74" s="17" t="n">
+      <c r="G74" s="13" t="n">
         <v>1166.666666666667</v>
       </c>
-      <c r="H74" s="19" t="n">
-        <v>47.22857142857143</v>
+      <c r="H74" s="15" t="n">
+        <v>50.05714285714286</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>615.6666666666667</v>
+        <v>582.6666666666667</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Ventrapragada S.O</t>
+          <t>Angaluru S.O</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>462</v>
+        <v>524</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>350</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>115.7142857142857</v>
+        <v>120.8571428571429</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3061,17 +3061,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Angaluru S.O</t>
+          <t>Ventrapragada S.O</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>350</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>112.2857142857143</v>
+        <v>116.8571428571429</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3094,17 +3094,17 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Vunguturu S.O (Krishna)</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C77" s="8" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
@@ -3118,26 +3118,26 @@
         <v>350</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>91.42857142857143</v>
+        <v>97.42857142857143</v>
       </c>
       <c r="I77" s="11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Rudrapaka S.O</t>
+          <t>Vunguturu S.O (Krishna)</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>341</v>
+        <v>396</v>
       </c>
       <c r="C78" s="8" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -3151,26 +3151,26 @@
         <v>350</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>87.42857142857143</v>
+        <v>92.28571428571428</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Moturu S.O</t>
+          <t>Mudunuru S.O</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -3184,26 +3184,26 @@
         <v>350</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>85.42857142857143</v>
+        <v>90.85714285714286</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Mudunuru S.O</t>
+          <t>Moturu S.O</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,43 +3217,43 @@
         <v>350</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>85.42857142857143</v>
+        <v>87.71428571428571</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>Mudinepalli S.O</t>
         </is>
       </c>
-      <c r="B81" s="13" t="n">
-        <v>582</v>
-      </c>
-      <c r="C81" s="13" t="n">
-        <v>321</v>
-      </c>
-      <c r="D81" s="14" t="n">
-        <v>261</v>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="B81" s="8" t="n">
+        <v>626</v>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>341</v>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F81" s="13" t="n">
+      <c r="F81" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G81" s="13" t="n">
+      <c r="G81" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="H81" s="15" t="n">
-        <v>74.57142857142857</v>
+      <c r="H81" s="10" t="n">
+        <v>81.42857142857143</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82">
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="C82" s="13" t="n">
         <v>132</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
@@ -3283,10 +3283,10 @@
         <v>350</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>68.28571428571428</v>
+        <v>74</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C83" s="13" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         <v>350</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>62.57142857142857</v>
+        <v>61.71428571428571</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
@@ -3349,59 +3349,59 @@
         <v>350</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>51.42857142857142</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="A85" s="12" t="inlineStr">
         <is>
           <t>Manikonda S.O</t>
         </is>
       </c>
-      <c r="B85" s="17" t="n">
-        <v>233</v>
-      </c>
-      <c r="C85" s="17" t="n">
-        <v>59</v>
-      </c>
-      <c r="D85" s="18" t="n">
-        <v>174</v>
-      </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="B85" s="13" t="n">
+        <v>245</v>
+      </c>
+      <c r="C85" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>183</v>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F85" s="17" t="n">
+      <c r="F85" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G85" s="17" t="n">
+      <c r="G85" s="13" t="n">
         <v>350</v>
       </c>
-      <c r="H85" s="19" t="n">
-        <v>49.71428571428572</v>
+      <c r="H85" s="15" t="n">
+        <v>52.28571428571429</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>Golvepalli (Zami) S.O</t>
+          <t>Tamirisa S.O</t>
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="C86" s="17" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,26 +3415,26 @@
         <v>350</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>41.42857142857143</v>
+        <v>41.14285714285714</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Tamirisa S.O</t>
+          <t>Golvepalli (Zami) S.O</t>
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="C87" s="17" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>350</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>40.28571428571428</v>
+        <v>40.85714285714286</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C88" s="17" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         <v>350</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>32</v>
+        <v>33.14285714285714</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89">
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>350</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>30.28571428571429</v>
+        <v>28.28571428571428</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>342</v>
+        <v>442</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>226</v>
+        <v>325</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>129.1428571428571</v>
+        <v>185.7142857142857</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3630,17 +3630,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>108.5714285714286</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3687,191 +3687,191 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>108</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Bhushanagulla B.O</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="C5" s="8" t="n">
+      <c r="B5" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>172</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>98.28571428571429</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>3</v>
+      <c r="D5" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>106.2857142857143</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Appikatla B.O</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>253</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>171</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>97.71428571428571</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>4</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Tummalapalli B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>103.4285714285714</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Moparru B.O</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>184</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>165</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>94.28571428571428</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>10</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Koyyagurapadu B.O</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>100.5714285714286</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Bokinala B.O</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>227</v>
-      </c>
-      <c r="C8" s="8" t="n">
+      <c r="B8" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>160</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>91.42857142857143</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>15</v>
+      <c r="D8" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>100.5714285714286</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Bollapadu B.O</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>189</v>
-      </c>
-      <c r="C9" s="8" t="n">
+      <c r="B9" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>159</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>90.85714285714286</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>16</v>
+      <c r="D9" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3885,26 +3885,26 @@
         <v>175</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>89.71428571428571</v>
+        <v>94.28571428571428</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3918,26 +3918,26 @@
         <v>175</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>89.71428571428571</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,26 +3951,26 @@
         <v>175</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>86.28571428571429</v>
+        <v>91.42857142857143</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3984,26 +3984,26 @@
         <v>175</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>85.14285714285714</v>
+        <v>90.85714285714286</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -4017,26 +4017,26 @@
         <v>175</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>84</v>
+        <v>90.28571428571428</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>161</v>
+        <v>272</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4050,26 +4050,26 @@
         <v>175</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>84</v>
+        <v>89.71428571428571</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -4083,26 +4083,26 @@
         <v>175</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>80.57142857142857</v>
+        <v>86.28571428571429</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -4116,92 +4116,92 @@
         <v>175</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>80</v>
+        <v>84.57142857142857</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Lingavaram B.O</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>147</v>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>72.57142857142857</v>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Nandigamalanka B.O</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>83.42857142857143</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Tenneru B.O</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>303</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>176</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>72.57142857142857</v>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Kanukollu B.O</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>82.28571428571428</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -4215,26 +4215,26 @@
         <v>175</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>72</v>
+        <v>78.85714285714286</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -4248,59 +4248,59 @@
         <v>175</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>72</v>
+        <v>77.71428571428571</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C22" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>76.57142857142857</v>
+      </c>
+      <c r="I22" s="11" t="n">
         <v>41</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>124</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>70.85714285714285</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,26 +4314,26 @@
         <v>175</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>68</v>
+        <v>73.71428571428571</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,26 +4347,26 @@
         <v>175</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>67.42857142857143</v>
+        <v>73.14285714285714</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,26 +4380,26 @@
         <v>175</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>66.28571428571428</v>
+        <v>72.57142857142857</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>175</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>65.71428571428571</v>
+        <v>72</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,26 +4446,26 @@
         <v>175</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>65.14285714285715</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,26 +4479,26 @@
         <v>175</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>65.14285714285715</v>
+        <v>69.14285714285714</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>147</v>
+        <v>318</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>175</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>69.14285714285714</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>175</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,59 +4578,59 @@
         <v>175</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>60</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="C32" s="13" t="n">
+        <v>123</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="I32" s="11" t="n">
         <v>58</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>103</v>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>58.85714285714285</v>
-      </c>
-      <c r="I32" s="11" t="n">
-        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,26 +4644,26 @@
         <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>63.42857142857142</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -4677,26 +4677,26 @@
         <v>175</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>55.42857142857143</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -4710,26 +4710,26 @@
         <v>175</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>54.85714285714286</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -4743,26 +4743,26 @@
         <v>175</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>54.28571428571428</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -4776,26 +4776,26 @@
         <v>175</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -4809,26 +4809,26 @@
         <v>175</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -4842,26 +4842,26 @@
         <v>175</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>53.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -4875,26 +4875,26 @@
         <v>175</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>53.14285714285715</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -4908,26 +4908,26 @@
         <v>175</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>52.57142857142857</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>111</v>
+        <v>205</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -4941,26 +4941,26 @@
         <v>175</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>51.42857142857142</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -4974,26 +4974,26 @@
         <v>175</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>51.42857142857142</v>
+        <v>56.57142857142857</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -5007,26 +5007,26 @@
         <v>175</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>50.85714285714285</v>
+        <v>56.57142857142857</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
@@ -5040,356 +5040,356 @@
         <v>175</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>50.85714285714285</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
+          <t>Polukonda B.O</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>55.42857142857143</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Lakshminarasimhapuram B.O</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>53.71428571428572</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Chinapalaparru B.O</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>53.71428571428572</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>53.71428571428572</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Edulamaddali B.O</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>194</v>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>53.14285714285715</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Koduru B.O</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>52.57142857142857</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
           <t>Pedaparupudi B.O</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n">
-        <v>124</v>
-      </c>
-      <c r="C46" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="D46" s="14" t="n">
+      <c r="B52" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Ramapuram B.O</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>51.42857142857142</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Siddantham B.O</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="n">
+        <v>186</v>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>50.85714285714285</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="C55" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="14" t="n">
         <v>88</v>
       </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H46" s="15" t="n">
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H55" s="15" t="n">
         <v>50.28571428571429</v>
       </c>
-      <c r="I46" s="11" t="n">
+      <c r="I55" s="11" t="n">
         <v>87</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="n">
-        <v>95</v>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>87</v>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G47" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H47" s="19" t="n">
-        <v>49.71428571428572</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>Komarru B.O</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="n">
-        <v>130</v>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>87</v>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G48" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>49.71428571428572</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>Chinayerukapadu B.O</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="n">
-        <v>121</v>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G49" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H49" s="19" t="n">
-        <v>49.14285714285715</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="n">
-        <v>93</v>
-      </c>
-      <c r="C50" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G50" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H50" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I50" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>Edulamaddali B.O</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="n">
-        <v>185</v>
-      </c>
-      <c r="C51" s="17" t="n">
-        <v>101</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G51" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H51" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>Chinapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="n">
-        <v>113</v>
-      </c>
-      <c r="C52" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D52" s="18" t="n">
-        <v>83</v>
-      </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G52" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H52" s="19" t="n">
-        <v>47.42857142857143</v>
-      </c>
-      <c r="I52" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>Serikalavapudi B.O</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="n">
-        <v>109</v>
-      </c>
-      <c r="C53" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>81</v>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G53" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>46.28571428571428</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>Koduru B.O</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="n">
-        <v>115</v>
-      </c>
-      <c r="C54" s="17" t="n">
-        <v>36</v>
-      </c>
-      <c r="D54" s="18" t="n">
-        <v>79</v>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G54" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H54" s="19" t="n">
-        <v>45.14285714285714</v>
-      </c>
-      <c r="I54" s="11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>Dandiganapudi B.O</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>79</v>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G55" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H55" s="19" t="n">
-        <v>45.14285714285714</v>
-      </c>
-      <c r="I55" s="11" t="n">
-        <v>96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -5403,10 +5403,10 @@
         <v>175</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>44.57142857142857</v>
+        <v>49.71428571428572</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
@@ -5416,13 +5416,13 @@
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C57" s="17" t="n">
         <v>42</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,26 +5436,26 @@
         <v>175</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>42.28571428571428</v>
+        <v>49.71428571428572</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,26 +5469,26 @@
         <v>175</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>41.71428571428572</v>
+        <v>47.42857142857143</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,59 +5502,59 @@
         <v>175</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>40.57142857142857</v>
+        <v>47.42857142857143</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>45.71428571428572</v>
+      </c>
+      <c r="I60" s="11" t="n">
         <v>95</v>
-      </c>
-      <c r="C60" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>65</v>
-      </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G60" s="17" t="n">
-        <v>175</v>
-      </c>
-      <c r="H60" s="19" t="n">
-        <v>37.14285714285715</v>
-      </c>
-      <c r="I60" s="11" t="n">
-        <v>110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,26 +5568,26 @@
         <v>175</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>35.42857142857142</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -5601,26 +5601,26 @@
         <v>175</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>34.28571428571428</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -5634,26 +5634,26 @@
         <v>175</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>33.14285714285714</v>
+        <v>38.85714285714285</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>175</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>31.42857142857143</v>
+        <v>38.85714285714285</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,10 +5700,10 @@
         <v>175</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>30.28571428571429</v>
+        <v>37.71428571428572</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66">
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5733,10 +5733,10 @@
         <v>175</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>30.28571428571429</v>
+        <v>34.28571428571428</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67">
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,26 +5766,26 @@
         <v>175</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>29.14285714285714</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>93</v>
+        <v>315</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>50</v>
+        <v>269</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>175</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>24.57142857142857</v>
+        <v>26.28571428571428</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C69" s="17" t="n">
         <v>20</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5832,26 +5832,26 @@
         <v>175</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>21.71428571428572</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -5865,26 +5865,26 @@
         <v>175</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>21.14285714285714</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Anamanapudi B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B71" s="17" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C71" s="17" t="n">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -5898,26 +5898,26 @@
         <v>175</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>5.714285714285714</v>
+        <v>23.42857142857143</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Anamanapudi B.O</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         <v>175</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>4.571428571428571</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73">
@@ -5944,13 +5944,13 @@
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C73" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -5964,10 +5964,10 @@
         <v>175</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-3.428571428571429</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -6047,17 +6047,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ventrapragada S.O</t>
+          <t>Angaluru S.O</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>462</v>
+        <v>524</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>350</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>115.7142857142857</v>
+        <v>120.8571428571429</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6080,17 +6080,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Angaluru S.O</t>
+          <t>Ventrapragada S.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>350</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>112.2857142857143</v>
+        <v>116.8571428571429</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6113,17 +6113,17 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Vunguturu S.O (Krishna)</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -6137,26 +6137,26 @@
         <v>350</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>91.42857142857143</v>
+        <v>97.42857142857143</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Rudrapaka S.O</t>
+          <t>Vunguturu S.O (Krishna)</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>341</v>
+        <v>396</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>350</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>87.42857142857143</v>
+        <v>92.28571428571428</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -6183,13 +6183,13 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6203,10 +6203,10 @@
         <v>350</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>85.42857142857143</v>
+        <v>90.85714285714286</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,43 +6236,43 @@
         <v>350</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>85.42857142857143</v>
+        <v>87.71428571428571</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Mudinepalli S.O</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>582</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>321</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>261</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="B8" s="8" t="n">
+        <v>626</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>341</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="H8" s="15" t="n">
-        <v>74.57142857142857</v>
+      <c r="H8" s="10" t="n">
+        <v>81.42857142857143</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>132</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -6302,10 +6302,10 @@
         <v>350</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>68.28571428571428</v>
+        <v>74</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         <v>350</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>62.57142857142857</v>
+        <v>61.71428571428571</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -6348,13 +6348,13 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6368,59 +6368,59 @@
         <v>350</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>51.42857142857142</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Manikonda S.O</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>233</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>59</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>174</v>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="B12" s="13" t="n">
+        <v>245</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>183</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="13" t="n">
         <v>350</v>
       </c>
-      <c r="H12" s="19" t="n">
-        <v>49.71428571428572</v>
+      <c r="H12" s="15" t="n">
+        <v>52.28571428571429</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Golvepalli (Zami) S.O</t>
+          <t>Tamirisa S.O</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,26 +6434,26 @@
         <v>350</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>41.42857142857143</v>
+        <v>41.14285714285714</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Tamirisa S.O</t>
+          <t>Golvepalli (Zami) S.O</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         <v>350</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>40.28571428571428</v>
+        <v>40.85714285714286</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -6480,13 +6480,13 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
         <v>350</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>32</v>
+        <v>33.14285714285714</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16">
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>350</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>30.28571428571429</v>
+        <v>28.28571428571428</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -6614,36 +6614,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
-        <v>1541</v>
-      </c>
-      <c r="C2" s="17" t="n">
-        <v>990</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <v>551</v>
-      </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="B2" s="13" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>584</v>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="13" t="n">
         <v>2000</v>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="13" t="n">
         <v>1166.666666666667</v>
       </c>
-      <c r="H2" s="19" t="n">
-        <v>47.22857142857143</v>
+      <c r="H2" s="15" t="n">
+        <v>50.05714285714286</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>615.6666666666667</v>
+        <v>582.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>342</v>
+        <v>442</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>226</v>
+        <v>325</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>129.1428571428571</v>
+        <v>185.7142857142857</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6756,17 +6756,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>108.5714285714286</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6793,13 +6793,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>108</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6826,13 +6826,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>19</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,26 +6846,26 @@
         <v>175</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>98.28571428571429</v>
+        <v>106.2857142857143</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6879,10 +6879,10 @@
         <v>175</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>97.71428571428571</v>
+        <v>103.4285714285714</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6986,26 +6986,26 @@
         <v>175</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>-3.428571428571429</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Anamanapudi B.O</t>
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7019,26 +7019,26 @@
         <v>175</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>4.571428571428571</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Anamanapudi B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7052,26 +7052,26 @@
         <v>175</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>5.714285714285714</v>
+        <v>23.42857142857143</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
@@ -7085,26 +7085,26 @@
         <v>175</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>21.14285714285714</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         <v>175</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>21.71428571428572</v>
+        <v>24.57142857142857</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -7201,17 +7201,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ventrapragada S.O</t>
+          <t>Angaluru S.O</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>462</v>
+        <v>524</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>350</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>115.7142857142857</v>
+        <v>120.8571428571429</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7234,17 +7234,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Angaluru S.O</t>
+          <t>Ventrapragada S.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>350</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>112.2857142857143</v>
+        <v>116.8571428571429</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7267,17 +7267,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vunguturu S.O (Krishna)</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7291,10 +7291,10 @@
         <v>350</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>91.42857142857143</v>
+        <v>97.42857142857143</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>350</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>30.28571428571429</v>
+        <v>28.28571428571428</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7431,26 +7431,26 @@
         <v>350</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>32</v>
+        <v>33.14285714285714</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Tamirisa S.O</t>
+          <t>Golvepalli (Zami) S.O</t>
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         <v>350</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>40.28571428571428</v>
+        <v>40.85714285714286</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>17491</v>
+        <v>18858</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>6056</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>11435</v>
+        <v>12472</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Offices" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BO Performance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO Performance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HO Performance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 5 BOs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bottom 5 BOs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 3 SOs" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bottom 3 SOs" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="All Offices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BO Performance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SO Performance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="HO Performance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Top 5 BOs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Bottom 5 BOs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Top 3 SOs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bottom 3 SOs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Summary" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Offices'!$A$1:$I$89</definedName>
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>185.7142857142857</v>
+        <v>157.1428571428571</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -652,17 +652,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>108.5714285714286</v>
+        <v>114.2857142857143</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>108</v>
+        <v>109.1428571428571</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -718,17 +718,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>175</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>106.2857142857143</v>
+        <v>107.4285714285714</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -751,17 +751,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>175</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>106.2857142857143</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -784,17 +784,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>175</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>100.5714285714286</v>
+        <v>104.5714285714286</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -817,17 +817,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>175</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>100.5714285714286</v>
+        <v>104.5714285714286</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
@@ -850,14 +850,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>175</v>
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -907,26 +907,26 @@
         <v>175</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>94.28571428571428</v>
+        <v>98.28571428571429</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -940,26 +940,26 @@
         <v>175</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>93.14285714285714</v>
+        <v>97.71428571428571</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
         <v>175</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>91.42857142857143</v>
+        <v>93.71428571428572</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1006,26 +1006,26 @@
         <v>175</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>90.85714285714286</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>177</v>
+        <v>217</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1039,26 +1039,26 @@
         <v>175</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>90.28571428571428</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1072,26 +1072,26 @@
         <v>175</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>89.71428571428571</v>
+        <v>92.57142857142857</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1105,26 +1105,26 @@
         <v>175</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>86.28571428571429</v>
+        <v>90.28571428571428</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1138,27 +1138,27 @@
         <v>175</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>84.57142857142857</v>
+        <v>89.71428571428571</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
+        <v>213</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>157</v>
       </c>
-      <c r="C18" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>146</v>
-      </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>BO</t>
@@ -1171,26 +1171,26 @@
         <v>175</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>83.42857142857143</v>
+        <v>89.71428571428571</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1204,92 +1204,92 @@
         <v>175</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>82.28571428571428</v>
+        <v>84.57142857142857</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Lingavaram B.O</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>158</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>138</v>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>78.85714285714286</v>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Putlacheruvu B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>80.57142857142857</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Gandhi Asramam B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>145</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>136</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>77.71428571428571</v>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Nandigamalanka B.O</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1303,26 +1303,26 @@
         <v>175</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>76.57142857142857</v>
+        <v>78.28571428571428</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,26 +1336,26 @@
         <v>175</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>73.71428571428571</v>
+        <v>77.14285714285715</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,26 +1369,26 @@
         <v>175</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>73.14285714285714</v>
+        <v>76.57142857142857</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
         <v>175</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>72.57142857142857</v>
+        <v>76.57142857142857</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,59 +1435,59 @@
         <v>175</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>72</v>
+        <v>75.42857142857143</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="C27" s="13" t="n">
+        <v>127</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>131</v>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>74.85714285714286</v>
+      </c>
+      <c r="I27" s="11" t="n">
         <v>44</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>125</v>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="I27" s="11" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         <v>175</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>69.14285714285714</v>
+        <v>73.14285714285714</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>175</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>69.14285714285714</v>
+        <v>72</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>175</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>67.42857142857143</v>
+        <v>70.28571428571428</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,26 +1600,26 @@
         <v>175</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>67.42857142857143</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1633,26 +1633,26 @@
         <v>175</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>66.85714285714286</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,26 +1666,26 @@
         <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>63.42857142857142</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -1699,26 +1699,26 @@
         <v>175</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>62.85714285714285</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -1732,26 +1732,26 @@
         <v>175</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>62.85714285714285</v>
+        <v>65.14285714285715</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>153</v>
+        <v>240</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -1765,26 +1765,26 @@
         <v>175</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>62.85714285714285</v>
+        <v>64</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -1798,59 +1798,59 @@
         <v>175</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>63.42857142857142</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="C38" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>62.85714285714285</v>
+      </c>
+      <c r="I38" s="11" t="n">
         <v>65</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>106</v>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>60.57142857142858</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -1864,26 +1864,26 @@
         <v>175</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>60</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1897,26 +1897,26 @@
         <v>175</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1930,27 +1930,27 @@
         <v>175</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C42" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D42" s="14" t="n">
         <v>105</v>
       </c>
-      <c r="D42" s="14" t="n">
-        <v>100</v>
-      </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
           <t>BO</t>
@@ -1963,26 +1963,26 @@
         <v>175</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>60</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
         <v>175</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>56.57142857142857</v>
+        <v>60</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C44" s="13" t="n">
         <v>22</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -2029,26 +2029,26 @@
         <v>175</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>56.57142857142857</v>
+        <v>59.42857142857143</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
@@ -2062,26 +2062,26 @@
         <v>175</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>58.28571428571428</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
@@ -2095,26 +2095,26 @@
         <v>175</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>55.42857142857143</v>
+        <v>57.71428571428572</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
@@ -2128,26 +2128,26 @@
         <v>175</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>57.71428571428572</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
@@ -2161,26 +2161,26 @@
         <v>175</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>57.71428571428572</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
         <v>175</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
@@ -2227,26 +2227,26 @@
         <v>175</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>53.14285714285715</v>
+        <v>55.42857142857143</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>39</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
@@ -2260,26 +2260,26 @@
         <v>175</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>52.57142857142857</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
         <v>128</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
@@ -2293,23 +2293,23 @@
         <v>175</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>52</v>
+        <v>53.71428571428572</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>90</v>
@@ -2333,82 +2333,82 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>Siddantham B.O</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="n">
-        <v>186</v>
-      </c>
-      <c r="C54" s="13" t="n">
-        <v>97</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>89</v>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G54" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>50.85714285714285</v>
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Addada B.O</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>49.71428571428572</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="n">
-        <v>96</v>
-      </c>
-      <c r="C55" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" s="14" t="n">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>49.71428571428572</v>
+      </c>
+      <c r="I55" s="11" t="n">
         <v>88</v>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>50.28571428571429</v>
-      </c>
-      <c r="I55" s="11" t="n">
-        <v>87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>87</v>
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         <v>175</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>49.71428571428572</v>
+        <v>47.42857142857143</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58">
@@ -2474,10 +2474,10 @@
         <v>110</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
         <v>175</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>47.42857142857143</v>
+        <v>46.85714285714286</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         <v>175</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>47.42857142857143</v>
+        <v>44.57142857142857</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60">
@@ -2540,10 +2540,10 @@
         <v>98</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -2557,26 +2557,26 @@
         <v>175</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>45.71428571428572</v>
+        <v>44.57142857142857</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,26 +2590,26 @@
         <v>175</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>40.57142857142857</v>
+        <v>44</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -2623,27 +2623,27 @@
         <v>175</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>40.57142857142857</v>
+        <v>43.42857142857143</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="C63" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D63" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="C63" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>68</v>
-      </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
           <t>BO</t>
@@ -2656,26 +2656,26 @@
         <v>175</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>38.85714285714285</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>175</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>38.85714285714285</v>
+        <v>41.71428571428572</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,26 +2722,26 @@
         <v>175</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>37.71428571428572</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2755,26 +2755,26 @@
         <v>175</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>34.28571428571428</v>
+        <v>40</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,26 +2788,26 @@
         <v>175</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>31.42857142857143</v>
+        <v>36.57142857142857</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>315</v>
+        <v>112</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>269</v>
+        <v>48</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2821,26 +2821,26 @@
         <v>175</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>26.28571428571428</v>
+        <v>36.57142857142857</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -2854,26 +2854,26 @@
         <v>175</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>24.57142857142857</v>
+        <v>32.57142857142858</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -2887,26 +2887,26 @@
         <v>175</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>24.57142857142857</v>
+        <v>30.85714285714285</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B71" s="17" t="n">
-        <v>167</v>
+        <v>317</v>
       </c>
       <c r="C71" s="17" t="n">
-        <v>126</v>
+        <v>272</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>175</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>23.42857142857143</v>
+        <v>25.71428571428571</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72">
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         <v>175</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>5.714285714285714</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C73" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-4</v>
+        <v>13</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         <v>175</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-2.285714285714286</v>
+        <v>7.428571428571429</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>1633</v>
+        <v>1779</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>1049</v>
+        <v>1130</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>584</v>
+        <v>649</v>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>1166.666666666667</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>50.05714285714286</v>
+        <v>55.62857142857143</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>582.6666666666667</v>
+        <v>517.6666666666667</v>
       </c>
     </row>
     <row r="75">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>350</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>120.8571428571429</v>
+        <v>136.5714285714286</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,92 +3085,92 @@
         <v>350</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>116.8571428571429</v>
+        <v>120</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>Rudrapaka S.O</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n">
-        <v>378</v>
-      </c>
-      <c r="C77" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="D77" s="9" t="n">
-        <v>341</v>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Mudunuru S.O</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>504</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>389</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n">
+      <c r="F77" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G77" s="8" t="n">
+      <c r="G77" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="H77" s="10" t="n">
-        <v>97.42857142857143</v>
-      </c>
-      <c r="I77" s="11" t="n">
-        <v>9</v>
+      <c r="H77" s="5" t="n">
+        <v>111.1428571428571</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Vunguturu S.O (Krishna)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="n">
-        <v>396</v>
-      </c>
-      <c r="C78" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="D78" s="9" t="n">
-        <v>323</v>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="B78" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>352</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F78" s="8" t="n">
+      <c r="F78" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G78" s="8" t="n">
+      <c r="G78" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="H78" s="10" t="n">
-        <v>92.28571428571428</v>
-      </c>
-      <c r="I78" s="11" t="n">
-        <v>27</v>
+      <c r="H78" s="5" t="n">
+        <v>100.5714285714286</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Mudunuru S.O</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         <v>350</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>90.85714285714286</v>
+        <v>98.85714285714286</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,26 +3217,26 @@
         <v>350</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>87.71428571428571</v>
+        <v>98.28571428571429</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Mudinepalli S.O</t>
+          <t>Indupalli S.O</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>626</v>
+        <v>463</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>341</v>
+        <v>132</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3250,43 +3250,43 @@
         <v>350</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>81.42857142857143</v>
+        <v>94.57142857142857</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t>Indupalli S.O</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="n">
-        <v>391</v>
-      </c>
-      <c r="C82" s="13" t="n">
-        <v>132</v>
-      </c>
-      <c r="D82" s="14" t="n">
-        <v>259</v>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Mudinepalli S.O</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>687</v>
+      </c>
+      <c r="C82" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>327</v>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F82" s="13" t="n">
+      <c r="F82" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G82" s="13" t="n">
+      <c r="G82" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="H82" s="15" t="n">
-        <v>74</v>
+      <c r="H82" s="10" t="n">
+        <v>93.42857142857143</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>91</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>261</v>
+        <v>322</v>
       </c>
       <c r="C83" s="13" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         <v>350</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>61.71428571428571</v>
+        <v>74.85714285714286</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>134</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
@@ -3349,10 +3349,10 @@
         <v>350</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="85">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="B85" s="13" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C85" s="13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
@@ -3382,26 +3382,26 @@
         <v>350</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>52.28571428571429</v>
+        <v>53.14285714285715</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>Tamirisa S.O</t>
+          <t>Golvepalli (Zami) S.O</t>
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="C86" s="17" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,26 +3415,26 @@
         <v>350</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>41.14285714285714</v>
+        <v>42</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Golvepalli (Zami) S.O</t>
+          <t>Tamirisa S.O</t>
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="C87" s="17" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>350</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>40.85714285714286</v>
+        <v>41.71428571428572</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C88" s="17" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         <v>350</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>33.14285714285714</v>
+        <v>34.85714285714286</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89">
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>350</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>28.28571428571428</v>
+        <v>28.85714285714286</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>185.7142857142857</v>
+        <v>157.1428571428571</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3630,17 +3630,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>108.5714285714286</v>
+        <v>114.2857142857143</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>108</v>
+        <v>109.1428571428571</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -3696,17 +3696,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>175</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>106.2857142857143</v>
+        <v>107.4285714285714</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -3729,17 +3729,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>175</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>106.2857142857143</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -3762,17 +3762,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>227</v>
+        <v>272</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>175</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>100.5714285714286</v>
+        <v>104.5714285714286</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -3795,17 +3795,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>175</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>100.5714285714286</v>
+        <v>104.5714285714286</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
@@ -3828,14 +3828,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>175</v>
@@ -3865,13 +3865,13 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3885,26 +3885,26 @@
         <v>175</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>94.28571428571428</v>
+        <v>98.28571428571429</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3918,26 +3918,26 @@
         <v>175</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>93.14285714285714</v>
+        <v>97.71428571428571</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,26 +3951,26 @@
         <v>175</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>91.42857142857143</v>
+        <v>93.71428571428572</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3984,26 +3984,26 @@
         <v>175</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>90.85714285714286</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>177</v>
+        <v>217</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -4017,26 +4017,26 @@
         <v>175</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>90.28571428571428</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4050,26 +4050,26 @@
         <v>175</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>89.71428571428571</v>
+        <v>92.57142857142857</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -4083,26 +4083,26 @@
         <v>175</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>86.28571428571429</v>
+        <v>90.28571428571428</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -4116,27 +4116,27 @@
         <v>175</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>84.57142857142857</v>
+        <v>89.71428571428571</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
+        <v>213</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>157</v>
       </c>
-      <c r="C18" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>146</v>
-      </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>BO</t>
@@ -4149,26 +4149,26 @@
         <v>175</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>83.42857142857143</v>
+        <v>89.71428571428571</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -4182,92 +4182,92 @@
         <v>175</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>82.28571428571428</v>
+        <v>84.57142857142857</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Lingavaram B.O</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>158</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>138</v>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>78.85714285714286</v>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Putlacheruvu B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>80.57142857142857</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Gandhi Asramam B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>145</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>136</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>77.71428571428571</v>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Nandigamalanka B.O</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -4281,26 +4281,26 @@
         <v>175</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>76.57142857142857</v>
+        <v>78.28571428571428</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,26 +4314,26 @@
         <v>175</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>73.71428571428571</v>
+        <v>77.14285714285715</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,26 +4347,26 @@
         <v>175</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>73.14285714285714</v>
+        <v>76.57142857142857</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>144</v>
+        <v>220</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,26 +4380,26 @@
         <v>175</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>72.57142857142857</v>
+        <v>76.57142857142857</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Putlacheruvu B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,59 +4413,59 @@
         <v>175</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>72</v>
+        <v>75.42857142857143</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="C27" s="13" t="n">
+        <v>127</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>131</v>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>74.85714285714286</v>
+      </c>
+      <c r="I27" s="11" t="n">
         <v>44</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>125</v>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="I27" s="11" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Garapadu B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
         <v>175</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>69.14285714285714</v>
+        <v>73.14285714285714</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>175</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>69.14285714285714</v>
+        <v>72</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>175</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>67.42857142857143</v>
+        <v>70.28571428571428</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,26 +4578,26 @@
         <v>175</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>67.42857142857143</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4611,26 +4611,26 @@
         <v>175</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>66.85714285714286</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,26 +4644,26 @@
         <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>63.42857142857142</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
         <v>142</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -4677,26 +4677,26 @@
         <v>175</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>62.85714285714285</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -4710,26 +4710,26 @@
         <v>175</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>62.85714285714285</v>
+        <v>65.14285714285715</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -4743,26 +4743,26 @@
         <v>175</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>62.85714285714285</v>
+        <v>64</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -4776,59 +4776,59 @@
         <v>175</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>63.42857142857142</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="C38" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>175</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>62.85714285714285</v>
+      </c>
+      <c r="I38" s="11" t="n">
         <v>65</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>106</v>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>60.57142857142858</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -4842,26 +4842,26 @@
         <v>175</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>60</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -4875,26 +4875,26 @@
         <v>175</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>61.14285714285715</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -4908,27 +4908,27 @@
         <v>175</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C42" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D42" s="14" t="n">
         <v>105</v>
       </c>
-      <c r="D42" s="14" t="n">
-        <v>100</v>
-      </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
           <t>BO</t>
@@ -4941,26 +4941,26 @@
         <v>175</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>60</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>121</v>
+        <v>212</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -4974,26 +4974,26 @@
         <v>175</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>56.57142857142857</v>
+        <v>60</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -5007,26 +5007,26 @@
         <v>175</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>56.57142857142857</v>
+        <v>59.42857142857143</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
@@ -5040,26 +5040,26 @@
         <v>175</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>58.28571428571428</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
@@ -5073,26 +5073,26 @@
         <v>175</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>55.42857142857143</v>
+        <v>57.71428571428572</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
@@ -5106,26 +5106,26 @@
         <v>175</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>57.71428571428572</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
@@ -5139,26 +5139,26 @@
         <v>175</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>57.71428571428572</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
@@ -5172,26 +5172,26 @@
         <v>175</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
@@ -5205,26 +5205,26 @@
         <v>175</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>53.14285714285715</v>
+        <v>55.42857142857143</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C51" s="13" t="n">
         <v>39</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
@@ -5238,26 +5238,26 @@
         <v>175</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>52.57142857142857</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
         <v>128</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
@@ -5271,23 +5271,23 @@
         <v>175</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>52</v>
+        <v>53.71428571428572</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>90</v>
@@ -5311,82 +5311,82 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>Siddantham B.O</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="n">
-        <v>186</v>
-      </c>
-      <c r="C54" s="13" t="n">
-        <v>97</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>89</v>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G54" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>50.85714285714285</v>
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Sankarshanapuram B.O</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>49.71428571428572</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="n">
-        <v>96</v>
-      </c>
-      <c r="C55" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" s="14" t="n">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>49.71428571428572</v>
+      </c>
+      <c r="I55" s="11" t="n">
         <v>88</v>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>50.28571428571429</v>
-      </c>
-      <c r="I55" s="11" t="n">
-        <v>87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>87</v>
@@ -5412,17 +5412,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
         <v>175</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>49.71428571428572</v>
+        <v>47.42857142857143</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58">
@@ -5452,10 +5452,10 @@
         <v>110</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,26 +5469,26 @@
         <v>175</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>47.42857142857143</v>
+        <v>46.85714285714286</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,10 +5502,10 @@
         <v>175</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>47.42857142857143</v>
+        <v>44.57142857142857</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60">
@@ -5518,10 +5518,10 @@
         <v>98</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -5535,26 +5535,26 @@
         <v>175</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>45.71428571428572</v>
+        <v>44.57142857142857</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,26 +5568,26 @@
         <v>175</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>40.57142857142857</v>
+        <v>44</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -5601,27 +5601,27 @@
         <v>175</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>40.57142857142857</v>
+        <v>43.42857142857143</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="C63" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D63" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="C63" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>68</v>
-      </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
           <t>BO</t>
@@ -5634,26 +5634,26 @@
         <v>175</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>38.85714285714285</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>175</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>38.85714285714285</v>
+        <v>41.71428571428572</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,26 +5700,26 @@
         <v>175</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>37.71428571428572</v>
+        <v>40.57142857142857</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Peyyeru B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5733,26 +5733,26 @@
         <v>175</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>34.28571428571428</v>
+        <v>40</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Peyyeru B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,26 +5766,26 @@
         <v>175</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>31.42857142857143</v>
+        <v>36.57142857142857</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Tarigoppula R.S. B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>315</v>
+        <v>112</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>269</v>
+        <v>48</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5799,26 +5799,26 @@
         <v>175</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>26.28571428571428</v>
+        <v>36.57142857142857</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B69" s="17" t="n">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5832,26 +5832,26 @@
         <v>175</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>24.57142857142857</v>
+        <v>32.57142857142858</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -5865,26 +5865,26 @@
         <v>175</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>24.57142857142857</v>
+        <v>30.85714285714285</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B71" s="17" t="n">
-        <v>167</v>
+        <v>317</v>
       </c>
       <c r="C71" s="17" t="n">
-        <v>126</v>
+        <v>272</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -5898,10 +5898,10 @@
         <v>175</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>23.42857142857143</v>
+        <v>25.71428571428571</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72">
@@ -5911,13 +5911,13 @@
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         <v>175</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>5.714285714285714</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73">
@@ -5944,13 +5944,13 @@
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C73" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-4</v>
+        <v>13</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -5964,10 +5964,10 @@
         <v>175</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-2.285714285714286</v>
+        <v>7.428571428571429</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>350</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>120.8571428571429</v>
+        <v>136.5714285714286</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6084,13 +6084,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,92 +6104,92 @@
         <v>350</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>116.8571428571429</v>
+        <v>120</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Rudrapaka S.O</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n">
-        <v>378</v>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>341</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mudunuru S.O</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>504</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>389</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="H4" s="10" t="n">
-        <v>97.42857142857143</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>9</v>
+      <c r="H4" s="5" t="n">
+        <v>111.1428571428571</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Vunguturu S.O (Krishna)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>396</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>323</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="B5" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>352</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="H5" s="10" t="n">
-        <v>92.28571428571428</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>27</v>
+      <c r="H5" s="5" t="n">
+        <v>100.5714285714286</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Mudunuru S.O</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6203,10 +6203,10 @@
         <v>350</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>90.85714285714286</v>
+        <v>98.85714285714286</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,26 +6236,26 @@
         <v>350</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>87.71428571428571</v>
+        <v>98.28571428571429</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Mudinepalli S.O</t>
+          <t>Indupalli S.O</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>626</v>
+        <v>463</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>341</v>
+        <v>132</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6269,43 +6269,43 @@
         <v>350</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>81.42857142857143</v>
+        <v>94.57142857142857</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Indupalli S.O</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>391</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>132</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>259</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Mudinepalli S.O</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>687</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>327</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="H9" s="15" t="n">
-        <v>74</v>
+      <c r="H9" s="10" t="n">
+        <v>93.42857142857143</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>91</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>261</v>
+        <v>322</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         <v>350</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>61.71428571428571</v>
+        <v>74.85714285714286</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>134</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -6348,13 +6348,13 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>350</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -6401,26 +6401,26 @@
         <v>350</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>52.28571428571429</v>
+        <v>53.14285714285715</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Tamirisa S.O</t>
+          <t>Golvepalli (Zami) S.O</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,26 +6434,26 @@
         <v>350</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>41.14285714285714</v>
+        <v>42</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Golvepalli (Zami) S.O</t>
+          <t>Tamirisa S.O</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         <v>350</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>40.85714285714286</v>
+        <v>41.71428571428572</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
@@ -6480,13 +6480,13 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
         <v>350</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>33.14285714285714</v>
+        <v>34.85714285714286</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>350</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>28.28571428571428</v>
+        <v>28.85714285714286</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1633</v>
+        <v>1779</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1049</v>
+        <v>1130</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>584</v>
+        <v>649</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>1166.666666666667</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>50.05714285714286</v>
+        <v>55.62857142857143</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>582.6666666666667</v>
+        <v>517.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>175</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>185.7142857142857</v>
+        <v>157.1428571428571</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6756,17 +6756,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>108.5714285714286</v>
+        <v>114.2857142857143</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6793,13 +6793,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>108</v>
+        <v>109.1428571428571</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6822,17 +6822,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>175</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>106.2857142857143</v>
+        <v>107.4285714285714</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -6855,17 +6855,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>175</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>103.4285714285714</v>
+        <v>106.2857142857143</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C2" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>-4</v>
+        <v>13</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
         <v>175</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>-2.285714285714286</v>
+        <v>7.428571428571429</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7019,26 +7019,26 @@
         <v>175</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>5.714285714285714</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Tarigoppula R.S. B.O</t>
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>167</v>
+        <v>317</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>126</v>
+        <v>272</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7052,10 +7052,10 @@
         <v>175</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>23.42857142857143</v>
+        <v>25.71428571428571</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
@@ -7065,13 +7065,13 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>20</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
@@ -7085,26 +7085,26 @@
         <v>175</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>24.57142857142857</v>
+        <v>30.85714285714285</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         <v>175</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>24.57142857142857</v>
+        <v>32.57142857142858</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>350</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>120.8571428571429</v>
+        <v>136.5714285714286</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>350</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>116.8571428571429</v>
+        <v>120</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7267,17 +7267,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Rudrapaka S.O</t>
+          <t>Mudunuru S.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>378</v>
+        <v>504</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7291,10 +7291,10 @@
         <v>350</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>97.42857142857143</v>
+        <v>111.1428571428571</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>350</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>28.28571428571428</v>
+        <v>28.85714285714286</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7431,26 +7431,26 @@
         <v>350</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>33.14285714285714</v>
+        <v>34.85714285714286</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Golvepalli (Zami) S.O</t>
+          <t>Tamirisa S.O</t>
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         <v>350</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>40.85714285714286</v>
+        <v>41.71428571428572</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>18858</v>
+        <v>20233</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>6386</v>
+        <v>6999</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>12472</v>
+        <v>13234</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -652,17 +652,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>114.2857142857143</v>
+        <v>121.7142857142857</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -685,17 +685,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>109.1428571428571</v>
+        <v>114.2857142857143</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -718,17 +718,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>175</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>107.4285714285714</v>
+        <v>109.1428571428571</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -751,17 +751,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>175</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>106.2857142857143</v>
+        <v>107.4285714285714</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -784,17 +784,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>272</v>
+        <v>205</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>175</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>104.5714285714286</v>
+        <v>106.2857142857143</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -817,14 +817,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>183</v>
@@ -949,17 +949,17 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
         <v>175</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>93.71428571428572</v>
+        <v>96</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1006,23 +1006,23 @@
         <v>175</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>93.14285714285714</v>
+        <v>93.71428571428572</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>163</v>
@@ -1048,17 +1048,17 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
         <v>175</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>92.57142857142857</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>23</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>175</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>84.57142857142857</v>
+        <v>86.28571428571429</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1411,17 +1411,17 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>175</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>75.42857142857143</v>
+        <v>74.85714285714286</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
         <v>175</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>74.85714285714286</v>
+        <v>74.28571428571429</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28">
@@ -1642,17 +1642,17 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Gunnanapudi B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,23 +1666,23 @@
         <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>67.42857142857143</v>
+        <v>68</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Gunnanapudi B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>118</v>
@@ -1807,17 +1807,17 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
         <v>175</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>62.85714285714285</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -1864,26 +1864,26 @@
         <v>175</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1897,26 +1897,26 @@
         <v>175</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1930,26 +1930,26 @@
         <v>175</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>60.57142857142858</v>
+        <v>60</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>206</v>
+        <v>126</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -1963,26 +1963,26 @@
         <v>175</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>60</v>
+        <v>59.42857142857143</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
         <v>175</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>60</v>
+        <v>59.42857142857143</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -2029,23 +2029,23 @@
         <v>175</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>59.42857142857143</v>
+        <v>58.28571428571428</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>102</v>
@@ -2137,17 +2137,17 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
@@ -2161,26 +2161,26 @@
         <v>175</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>57.71428571428572</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
         <v>175</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>55.42857142857143</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>39</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
@@ -2227,26 +2227,26 @@
         <v>175</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>55.42857142857143</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
@@ -2260,26 +2260,26 @@
         <v>175</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>54.28571428571428</v>
+        <v>53.71428571428572</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
         <v>175</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>53.14285714285715</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53">
@@ -2309,10 +2309,10 @@
         <v>128</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
         <v>175</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>51.42857142857142</v>
+        <v>50.85714285714285</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54">
@@ -2434,17 +2434,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,26 +2458,26 @@
         <v>175</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>47.42857142857143</v>
+        <v>46.85714285714286</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         <v>175</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>46.85714285714286</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59">
@@ -2764,17 +2764,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,23 +2788,23 @@
         <v>175</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>36.57142857142857</v>
+        <v>37.71428571428572</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="D68" s="18" t="n">
         <v>64</v>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>1166.666666666667</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>55.62857142857143</v>
+        <v>55.45714285714285</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>517.6666666666667</v>
+        <v>519.6666666666667</v>
       </c>
     </row>
     <row r="75">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>350</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>136.5714285714286</v>
+        <v>136.2857142857143</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3065,10 +3065,10 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D76" s="4" t="n">
         <v>420</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>76</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3151,59 +3151,59 @@
         <v>350</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>100.5714285714286</v>
+        <v>103.7142857142857</v>
       </c>
       <c r="I78" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Rudrapaka S.O</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="n">
-        <v>384</v>
-      </c>
-      <c r="C79" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="D79" s="9" t="n">
-        <v>346</v>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Moturu S.O</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F79" s="8" t="n">
+      <c r="F79" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G79" s="8" t="n">
+      <c r="G79" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="H79" s="10" t="n">
-        <v>98.85714285714286</v>
-      </c>
-      <c r="I79" s="11" t="n">
-        <v>4</v>
+      <c r="H79" s="5" t="n">
+        <v>103.4285714285714</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Moturu S.O</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>422</v>
+        <v>385</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         <v>350</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>98.28571428571429</v>
+        <v>99.14285714285714</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="C81" s="8" t="n">
         <v>132</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         <v>350</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>94.57142857142857</v>
+        <v>97.42857142857143</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C82" s="8" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D82" s="9" t="n">
         <v>327</v>
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C84" s="13" t="n">
         <v>291</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
@@ -3349,10 +3349,10 @@
         <v>350</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>58.85714285714285</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85">
@@ -3365,10 +3365,10 @@
         <v>253</v>
       </c>
       <c r="C85" s="13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         <v>350</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>53.14285714285715</v>
+        <v>52.85714285714286</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86">
@@ -3497,10 +3497,10 @@
         <v>187</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>350</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>28.85714285714286</v>
+        <v>28.28571428571428</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -3630,17 +3630,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>114.2857142857143</v>
+        <v>121.7142857142857</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3663,17 +3663,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>109.1428571428571</v>
+        <v>114.2857142857143</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -3696,17 +3696,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>175</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>107.4285714285714</v>
+        <v>109.1428571428571</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -3729,17 +3729,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>175</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>106.2857142857143</v>
+        <v>107.4285714285714</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -3762,17 +3762,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>272</v>
+        <v>205</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>175</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>104.5714285714286</v>
+        <v>106.2857142857143</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -3795,14 +3795,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>183</v>
@@ -3927,17 +3927,17 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,26 +3951,26 @@
         <v>175</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>93.71428571428572</v>
+        <v>96</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3984,23 +3984,23 @@
         <v>175</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>93.14285714285714</v>
+        <v>93.71428571428572</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>163</v>
@@ -4030,13 +4030,13 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>55</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>175</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>92.57142857142857</v>
+        <v>93.14285714285714</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>23</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -4182,10 +4182,10 @@
         <v>175</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>84.57142857142857</v>
+        <v>86.28571428571429</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -4389,17 +4389,17 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>175</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>75.42857142857143</v>
+        <v>74.85714285714286</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
         <v>175</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>74.85714285714286</v>
+        <v>74.28571428571429</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28">
@@ -4624,13 +4624,13 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>42</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>67.42857142857143</v>
+        <v>68</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -4785,17 +4785,17 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
         <v>175</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>62.85714285714285</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
@@ -4825,10 +4825,10 @@
         <v>161</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -4842,26 +4842,26 @@
         <v>175</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>60.57142857142858</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -4875,26 +4875,26 @@
         <v>175</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>61.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -4908,26 +4908,26 @@
         <v>175</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>60.57142857142858</v>
+        <v>60</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -4941,26 +4941,26 @@
         <v>175</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>60</v>
+        <v>59.42857142857143</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>212</v>
+        <v>126</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -4974,26 +4974,26 @@
         <v>175</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>60</v>
+        <v>59.42857142857143</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -5007,23 +5007,23 @@
         <v>175</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>59.42857142857143</v>
+        <v>58.28571428571428</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>102</v>
@@ -5082,14 +5082,14 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>101</v>
@@ -5115,17 +5115,17 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
@@ -5139,26 +5139,26 @@
         <v>175</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>57.71428571428572</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Koduru B.O</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
@@ -5172,26 +5172,26 @@
         <v>175</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>57.14285714285714</v>
+        <v>55.42857142857143</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Koduru B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>39</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
@@ -5205,26 +5205,26 @@
         <v>175</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>55.42857142857143</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
@@ -5238,26 +5238,26 @@
         <v>175</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>54.28571428571428</v>
+        <v>53.71428571428572</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
@@ -5271,10 +5271,10 @@
         <v>175</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>53.71428571428572</v>
+        <v>53.14285714285715</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53">
@@ -5287,10 +5287,10 @@
         <v>128</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
@@ -5304,10 +5304,10 @@
         <v>175</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>51.42857142857142</v>
+        <v>50.85714285714285</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54">
@@ -5412,17 +5412,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,26 +5436,26 @@
         <v>175</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>47.42857142857143</v>
+        <v>46.85714285714286</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>175</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>46.85714285714286</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59">
@@ -5742,17 +5742,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Chandrala B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,23 +5766,23 @@
         <v>175</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>36.57142857142857</v>
+        <v>37.71428571428572</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Chandrala B.O</t>
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="D68" s="18" t="n">
         <v>64</v>
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>350</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>136.5714285714286</v>
+        <v>136.2857142857143</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>420</v>
@@ -6150,13 +6150,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>76</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6170,59 +6170,59 @@
         <v>350</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>100.5714285714286</v>
+        <v>103.7142857142857</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Rudrapaka S.O</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>384</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>346</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Moturu S.O</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="H6" s="10" t="n">
-        <v>98.85714285714286</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>4</v>
+      <c r="H6" s="5" t="n">
+        <v>103.4285714285714</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Moturu S.O</t>
+          <t>Rudrapaka S.O</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>422</v>
+        <v>385</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         <v>350</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>98.28571428571429</v>
+        <v>99.14285714285714</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>132</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6269,10 +6269,10 @@
         <v>350</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>94.57142857142857</v>
+        <v>97.42857142857143</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>327</v>
@@ -6348,13 +6348,13 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>291</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>350</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>58.85714285714285</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
@@ -6384,10 +6384,10 @@
         <v>253</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         <v>350</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>53.14285714285715</v>
+        <v>52.85714285714286</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -6516,10 +6516,10 @@
         <v>187</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>350</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>28.85714285714286</v>
+        <v>28.28571428571428</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>1166.666666666667</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>55.62857142857143</v>
+        <v>55.45714285714285</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>517.6666666666667</v>
+        <v>519.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6756,17 +6756,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>175</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>114.2857142857143</v>
+        <v>121.7142857142857</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6789,17 +6789,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>175</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>109.1428571428571</v>
+        <v>114.2857142857143</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6822,17 +6822,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>175</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>107.4285714285714</v>
+        <v>109.1428571428571</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -6855,17 +6855,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>175</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>106.2857142857143</v>
+        <v>107.4285714285714</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>350</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>136.5714285714286</v>
+        <v>136.2857142857143</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>420</v>
@@ -7381,10 +7381,10 @@
         <v>187</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>350</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>28.85714285714286</v>
+        <v>28.28571428571428</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>20233</v>
+        <v>20325</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>6999</v>
+        <v>7038</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>13234</v>
+        <v>13287</v>
       </c>
     </row>
   </sheetData>
